--- a/SCE_detected.xlsx
+++ b/SCE_detected.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G349"/>
+  <dimension ref="A1:G314"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -784,12 +784,10 @@
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Translocation</t>
-        </is>
-      </c>
-      <c r="G13" t="n">
-        <v>6.25</v>
-      </c>
+          <t>SCE</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1371,11 +1369,11 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>chr13</t>
+          <t>chr2</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>108600000</v>
+        <v>65600000</v>
       </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
@@ -1402,7 +1400,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>65600000</v>
+        <v>110600000</v>
       </c>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
@@ -1425,11 +1423,11 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>chr2</t>
+          <t>chr3</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>110600000</v>
+        <v>71200000</v>
       </c>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
@@ -1456,7 +1454,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>71200000</v>
+        <v>75000000</v>
       </c>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
@@ -1483,7 +1481,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>75000000</v>
+        <v>148600000</v>
       </c>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
@@ -1506,11 +1504,11 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>chr3</t>
+          <t>chr4</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>148600000</v>
+        <v>162800000</v>
       </c>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
@@ -1537,7 +1535,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>162800000</v>
+        <v>181200000</v>
       </c>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
@@ -1560,11 +1558,11 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>chr4</t>
+          <t>chr5</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>181200000</v>
+        <v>161200000</v>
       </c>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
@@ -1587,11 +1585,11 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>chr5</t>
+          <t>chr6</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>161200000</v>
+        <v>119000000</v>
       </c>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
@@ -1614,11 +1612,11 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>chr6</t>
+          <t>chr8</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>119000000</v>
+        <v>123800000</v>
       </c>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
@@ -1641,11 +1639,11 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>chr8</t>
+          <t>chr9</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>123800000</v>
+        <v>14400000</v>
       </c>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
@@ -1672,7 +1670,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>14400000</v>
+        <v>129000000</v>
       </c>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
@@ -1690,16 +1688,16 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G08</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G12</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>chr9</t>
+          <t>chr1</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>129000000</v>
+        <v>194800000</v>
       </c>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
@@ -1722,11 +1720,11 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>chr1</t>
+          <t>chr14</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>194800000</v>
+        <v>53000000</v>
       </c>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
@@ -1749,11 +1747,11 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>chr14</t>
+          <t>chr16</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>53000000</v>
+        <v>47000000</v>
       </c>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
@@ -1776,16 +1774,18 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>chr16</t>
+          <t>chr17</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>47000000</v>
-      </c>
-      <c r="E50" t="inlineStr"/>
+        <v>28200000</v>
+      </c>
+      <c r="E50" t="n">
+        <v>34600000</v>
+      </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>SCE</t>
+          <t>Inversion</t>
         </is>
       </c>
       <c r="G50" t="inlineStr"/>
@@ -1807,7 +1807,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>31800000</v>
+        <v>53000000</v>
       </c>
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
@@ -1830,11 +1830,11 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>chr17</t>
+          <t>chr2</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>34600000</v>
+        <v>132800000</v>
       </c>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
@@ -1857,19 +1857,21 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>chr17</t>
+          <t>chr20</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>53000000</v>
+        <v>31200000</v>
       </c>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
-          <t>SCE</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr"/>
+          <t>Translocation</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
+        <v>9.380000000000001</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1884,11 +1886,11 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>chr2</t>
+          <t>chr20</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>132800000</v>
+        <v>31400000</v>
       </c>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
@@ -1911,21 +1913,19 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>chr20</t>
+          <t>chr22</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>31200000</v>
+        <v>19000000</v>
       </c>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Translocation</t>
-        </is>
-      </c>
-      <c r="G55" t="n">
-        <v>9.380000000000001</v>
-      </c>
+          <t>SCE</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1940,21 +1940,19 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>chr20</t>
+          <t>chr22</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>31400000</v>
+        <v>44400000</v>
       </c>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Translocation</t>
-        </is>
-      </c>
-      <c r="G56" t="n">
-        <v>6.25</v>
-      </c>
+          <t>SCE</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1969,11 +1967,11 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>chr22</t>
+          <t>chr3</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>21400000</v>
+        <v>181400000</v>
       </c>
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
@@ -1996,11 +1994,11 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>chr22</t>
+          <t>chr9</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>44400000</v>
+        <v>29200000</v>
       </c>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
@@ -2023,11 +2021,11 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>chr3</t>
+          <t>chrX</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>181400000</v>
+        <v>4000000</v>
       </c>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
@@ -2045,16 +2043,16 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G12</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G13</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>chr9</t>
+          <t>chr1</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>29200000</v>
+        <v>73000000</v>
       </c>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
@@ -2072,16 +2070,16 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G12</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G13</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>chrX</t>
+          <t>chr13</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>4000000</v>
+        <v>105600000</v>
       </c>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
@@ -2104,11 +2102,11 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>chr1</t>
+          <t>chr4</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>73000000</v>
+        <v>91000000</v>
       </c>
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
@@ -2131,11 +2129,11 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>chr13</t>
+          <t>chr6</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>105600000</v>
+        <v>116200000</v>
       </c>
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
@@ -2153,16 +2151,16 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G13</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G16</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>chr4</t>
+          <t>chr1</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>91000000</v>
+        <v>91800000</v>
       </c>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
@@ -2180,16 +2178,16 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G13</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G16</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>chr6</t>
+          <t>chr13</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>116200000</v>
+        <v>30200000</v>
       </c>
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
@@ -2212,11 +2210,11 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>chr1</t>
+          <t>chr14</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>91800000</v>
+        <v>99000000</v>
       </c>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
@@ -2239,11 +2237,11 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>chr13</t>
+          <t>chr18</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>30200000</v>
+        <v>68200000</v>
       </c>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
@@ -2266,11 +2264,11 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>chr14</t>
+          <t>chr19</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>99000000</v>
+        <v>7600000</v>
       </c>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
@@ -2293,11 +2291,11 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>chr18</t>
+          <t>chr2</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>68200000</v>
+        <v>163600000</v>
       </c>
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
@@ -2320,11 +2318,11 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>chr19</t>
+          <t>chr5</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>7600000</v>
+        <v>12600000</v>
       </c>
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
@@ -2347,11 +2345,11 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>chr2</t>
+          <t>chr6</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>163600000</v>
+        <v>31200000</v>
       </c>
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
@@ -2374,11 +2372,11 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>chr4</t>
+          <t>chr6</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>91200000</v>
+        <v>39400000</v>
       </c>
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
@@ -2396,16 +2394,16 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G16</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G18</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>chr4</t>
+          <t>chr1</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>94600000</v>
+        <v>147600000</v>
       </c>
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
@@ -2423,16 +2421,16 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G16</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G18</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>chr5</t>
+          <t>chr10</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>12600000</v>
+        <v>72800000</v>
       </c>
       <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
@@ -2450,24 +2448,26 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G16</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G18</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>chr6</t>
+          <t>chr16</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>31200000</v>
+        <v>47600000</v>
       </c>
       <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
-          <t>SCE</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr"/>
+          <t>Translocation</t>
+        </is>
+      </c>
+      <c r="G75" t="n">
+        <v>9.380000000000001</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2477,16 +2477,16 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G16</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G18</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>chr6</t>
+          <t>chr18</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>39400000</v>
+        <v>76200000</v>
       </c>
       <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
@@ -2509,11 +2509,11 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>chr1</t>
+          <t>chr2</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>147600000</v>
+        <v>33400000</v>
       </c>
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
@@ -2536,11 +2536,11 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>chr10</t>
+          <t>chr21</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>72800000</v>
+        <v>25600000</v>
       </c>
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
@@ -2563,11 +2563,11 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>chr16</t>
+          <t>chr8</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>47600000</v>
+        <v>65400000</v>
       </c>
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr">
@@ -2576,7 +2576,7 @@
         </is>
       </c>
       <c r="G79" t="n">
-        <v>9.380000000000001</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="80">
@@ -2592,11 +2592,11 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>chr18</t>
+          <t>chrX</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>76200000</v>
+        <v>32600000</v>
       </c>
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr">
@@ -2614,16 +2614,16 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G18</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G19</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>chr2</t>
+          <t>chr11</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>33400000</v>
+        <v>56800000</v>
       </c>
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
@@ -2641,16 +2641,16 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G18</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G19</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>chr21</t>
+          <t>chr14</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>25600000</v>
+        <v>36600000</v>
       </c>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr">
@@ -2668,26 +2668,24 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G18</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G19</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>chr8</t>
+          <t>chr15</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>65400000</v>
+        <v>81600000</v>
       </c>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Translocation</t>
-        </is>
-      </c>
-      <c r="G83" t="n">
-        <v>6.25</v>
-      </c>
+          <t>SCE</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -2697,16 +2695,16 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G18</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G19</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>chrX</t>
+          <t>chr16</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>32600000</v>
+        <v>70200000</v>
       </c>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr">
@@ -2729,11 +2727,11 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>chr10</t>
+          <t>chr18</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>105200000</v>
+        <v>33000000</v>
       </c>
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
@@ -2756,11 +2754,11 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>chr10</t>
+          <t>chr2</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>108800000</v>
+        <v>11000000</v>
       </c>
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr">
@@ -2783,11 +2781,11 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>chr11</t>
+          <t>chr2</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>56800000</v>
+        <v>154000000</v>
       </c>
       <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr">
@@ -2810,11 +2808,11 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>chr14</t>
+          <t>chr2</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>36600000</v>
+        <v>160200000</v>
       </c>
       <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr">
@@ -2837,11 +2835,11 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>chr14</t>
+          <t>chr21</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>81800000</v>
+        <v>18000000</v>
       </c>
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr">
@@ -2864,11 +2862,11 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>chr14</t>
+          <t>chr22</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>88000000</v>
+        <v>25400000</v>
       </c>
       <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr">
@@ -2891,11 +2889,11 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>chr15</t>
+          <t>chr3</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>81600000</v>
+        <v>36000000</v>
       </c>
       <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr">
@@ -2913,16 +2911,16 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G19</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G20</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>chr16</t>
+          <t>chr12</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>70200000</v>
+        <v>4800000</v>
       </c>
       <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr">
@@ -2940,16 +2938,16 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G19</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G20</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>chr18</t>
+          <t>chr12</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>33000000</v>
+        <v>116000000</v>
       </c>
       <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr">
@@ -2967,16 +2965,16 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G19</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G20</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>chr2</t>
+          <t>chr14</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>11000000</v>
+        <v>50000000</v>
       </c>
       <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr">
@@ -2994,16 +2992,16 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G19</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G20</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>chr2</t>
+          <t>chr15</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>154000000</v>
+        <v>78800000</v>
       </c>
       <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr">
@@ -3021,16 +3019,16 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G19</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G20</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>chr2</t>
+          <t>chr19</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>160200000</v>
+        <v>1800000</v>
       </c>
       <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr">
@@ -3048,16 +3046,16 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G19</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G20</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>chr21</t>
+          <t>chr2</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>18000000</v>
+        <v>213400000</v>
       </c>
       <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr">
@@ -3075,24 +3073,26 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G19</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G20</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>chr22</t>
+          <t>chr20</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>25400000</v>
+        <v>31200000</v>
       </c>
       <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr">
         <is>
-          <t>SCE</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr"/>
+          <t>Translocation</t>
+        </is>
+      </c>
+      <c r="G98" t="n">
+        <v>9.380000000000001</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3102,16 +3102,16 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G19</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G20</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>chr3</t>
+          <t>chr20</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>36000000</v>
+        <v>31800000</v>
       </c>
       <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr">
@@ -3129,16 +3129,16 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G19</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G20</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>chr3</t>
+          <t>chr4</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>94800000</v>
+        <v>156000000</v>
       </c>
       <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr">
@@ -3156,16 +3156,16 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G19</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G20</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>chr3</t>
+          <t>chr9</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>97600000</v>
+        <v>80200000</v>
       </c>
       <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr">
@@ -3183,26 +3183,24 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G19</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G24</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>chr6</t>
+          <t>chr1</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>90800000</v>
+        <v>9400000</v>
       </c>
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Translocation</t>
-        </is>
-      </c>
-      <c r="G102" t="n">
-        <v>9.380000000000001</v>
-      </c>
+          <t>SCE</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -3212,16 +3210,16 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G19</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G24</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>chr6</t>
+          <t>chr18</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>95800000</v>
+        <v>30800000</v>
       </c>
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr">
@@ -3239,16 +3237,16 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G19</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G24</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>chr7</t>
+          <t>chr5</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>55800000</v>
+        <v>60400000</v>
       </c>
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr">
@@ -3266,16 +3264,16 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G19</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G24</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>chr7</t>
+          <t>chr9</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>72200000</v>
+        <v>83800000</v>
       </c>
       <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr">
@@ -3293,16 +3291,16 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G20</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G25</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>chr12</t>
+          <t>chr1</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>4800000</v>
+        <v>35600000</v>
       </c>
       <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr">
@@ -3320,16 +3318,16 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G20</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G25</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>chr12</t>
+          <t>chr10</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>116000000</v>
+        <v>75600000</v>
       </c>
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr">
@@ -3347,16 +3345,16 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G20</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G25</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>chr14</t>
+          <t>chr11</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>50000000</v>
+        <v>18400000</v>
       </c>
       <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr">
@@ -3374,16 +3372,16 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G20</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G25</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>chr15</t>
+          <t>chr12</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>78800000</v>
+        <v>1800000</v>
       </c>
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr">
@@ -3401,16 +3399,16 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G20</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G25</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>chr19</t>
+          <t>chr12</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>1800000</v>
+        <v>12800000</v>
       </c>
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr">
@@ -3428,16 +3426,16 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G20</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G25</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>chr2</t>
+          <t>chr12</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>213400000</v>
+        <v>43600000</v>
       </c>
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr">
@@ -3455,26 +3453,24 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G20</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G25</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>chr20</t>
+          <t>chr2</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>31200000</v>
+        <v>182400000</v>
       </c>
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Translocation</t>
-        </is>
-      </c>
-      <c r="G112" t="n">
-        <v>9.380000000000001</v>
-      </c>
+          <t>SCE</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -3484,26 +3480,24 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G20</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G25</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>chr20</t>
+          <t>chr5</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>31800000</v>
+        <v>119800000</v>
       </c>
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Translocation</t>
-        </is>
-      </c>
-      <c r="G113" t="n">
-        <v>6.25</v>
-      </c>
+          <t>SCE</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -3513,16 +3507,16 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G20</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G25</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>chr4</t>
+          <t>chrX</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>156000000</v>
+        <v>81000000</v>
       </c>
       <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr">
@@ -3540,16 +3534,16 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G20</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G26</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>chr9</t>
+          <t>chr11</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>80200000</v>
+        <v>46000000</v>
       </c>
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr">
@@ -3567,16 +3561,16 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G24</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G26</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>chr1</t>
+          <t>chr11</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>9400000</v>
+        <v>85600000</v>
       </c>
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr">
@@ -3594,16 +3588,16 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G24</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G26</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>chr18</t>
+          <t>chr12</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>30800000</v>
+        <v>72600000</v>
       </c>
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr">
@@ -3621,16 +3615,16 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G24</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G26</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>chr5</t>
+          <t>chr14</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>60400000</v>
+        <v>76600000</v>
       </c>
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr">
@@ -3648,16 +3642,16 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G24</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G26</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>chr9</t>
+          <t>chr16</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>83800000</v>
+        <v>30200000</v>
       </c>
       <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr">
@@ -3675,16 +3669,16 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G25</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G26</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>chr1</t>
+          <t>chr18</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>35600000</v>
+        <v>45600000</v>
       </c>
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr">
@@ -3702,16 +3696,16 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G25</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G26</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>chr10</t>
+          <t>chr19</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>75600000</v>
+        <v>52400000</v>
       </c>
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr">
@@ -3729,16 +3723,16 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G25</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G26</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>chr11</t>
+          <t>chr2</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>18400000</v>
+        <v>69400000</v>
       </c>
       <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr">
@@ -3756,16 +3750,16 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G25</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G26</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>chr12</t>
+          <t>chr5</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>1800000</v>
+        <v>142600000</v>
       </c>
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr">
@@ -3783,16 +3777,16 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G25</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G26</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>chr12</t>
+          <t>chr6</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>12800000</v>
+        <v>55400000</v>
       </c>
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr">
@@ -3810,24 +3804,26 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G25</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G26</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>chr12</t>
+          <t>chr8</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>43600000</v>
+        <v>65400000</v>
       </c>
       <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr">
         <is>
-          <t>SCE</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr"/>
+          <t>Translocation</t>
+        </is>
+      </c>
+      <c r="G125" t="n">
+        <v>6.25</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -3837,16 +3833,16 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G25</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G27</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>chr2</t>
+          <t>chr1</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>182400000</v>
+        <v>30200000</v>
       </c>
       <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr">
@@ -3864,16 +3860,16 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G25</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G27</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>chr5</t>
+          <t>chr1</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>119800000</v>
+        <v>182400000</v>
       </c>
       <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr">
@@ -3891,16 +3887,16 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G25</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G27</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>chrX</t>
+          <t>chr10</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>81000000</v>
+        <v>43200000</v>
       </c>
       <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr">
@@ -3918,7 +3914,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G26</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G27</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -3927,7 +3923,7 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>46000000</v>
+        <v>127200000</v>
       </c>
       <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr">
@@ -3945,16 +3941,16 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G26</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G27</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>chr11</t>
+          <t>chr13</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>85600000</v>
+        <v>75800000</v>
       </c>
       <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr">
@@ -3972,16 +3968,16 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G26</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G27</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>chr12</t>
+          <t>chr16</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>72600000</v>
+        <v>53000000</v>
       </c>
       <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr">
@@ -3999,16 +3995,16 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G26</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G27</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>chr14</t>
+          <t>chr18</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>76600000</v>
+        <v>24400000</v>
       </c>
       <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr">
@@ -4026,16 +4022,16 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G26</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G27</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>chr16</t>
+          <t>chr18</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>30200000</v>
+        <v>58400000</v>
       </c>
       <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr">
@@ -4053,16 +4049,16 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G26</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G27</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>chr18</t>
+          <t>chr2</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>45600000</v>
+        <v>29400000</v>
       </c>
       <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr">
@@ -4080,16 +4076,16 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G26</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G27</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>chr19</t>
+          <t>chr3</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>52400000</v>
+        <v>66800000</v>
       </c>
       <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr">
@@ -4107,16 +4103,16 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G26</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G28</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>chr2</t>
+          <t>chr1</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>69400000</v>
+        <v>30800000</v>
       </c>
       <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr">
@@ -4134,16 +4130,16 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G26</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G28</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>chr5</t>
+          <t>chr10</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>142600000</v>
+        <v>16800000</v>
       </c>
       <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr">
@@ -4161,16 +4157,16 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G26</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G28</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>chr6</t>
+          <t>chr11</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>55400000</v>
+        <v>63000000</v>
       </c>
       <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr">
@@ -4188,26 +4184,24 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G26</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G28</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>chr8</t>
+          <t>chr12</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>65400000</v>
+        <v>99600000</v>
       </c>
       <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Translocation</t>
-        </is>
-      </c>
-      <c r="G139" t="n">
-        <v>6.25</v>
-      </c>
+          <t>SCE</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -4217,16 +4211,16 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G27</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G28</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>chr1</t>
+          <t>chr21</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>30200000</v>
+        <v>25800000</v>
       </c>
       <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr">
@@ -4244,16 +4238,16 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G27</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G28</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>chr1</t>
+          <t>chr22</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>182400000</v>
+        <v>42200000</v>
       </c>
       <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr">
@@ -4271,16 +4265,16 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G27</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G28</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>chr10</t>
+          <t>chr4</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>43200000</v>
+        <v>41000000</v>
       </c>
       <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr">
@@ -4298,16 +4292,16 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G27</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G28</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>chr11</t>
+          <t>chr7</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>127200000</v>
+        <v>5600000</v>
       </c>
       <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr">
@@ -4325,16 +4319,16 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G27</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G28</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>chr13</t>
+          <t>chr7</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>75800000</v>
+        <v>19800000</v>
       </c>
       <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr">
@@ -4352,16 +4346,16 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G27</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G30</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>chr16</t>
+          <t>chr1</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>53000000</v>
+        <v>219400000</v>
       </c>
       <c r="E145" t="inlineStr"/>
       <c r="F145" t="inlineStr">
@@ -4379,16 +4373,16 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G27</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G30</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>chr18</t>
+          <t>chr12</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>24400000</v>
+        <v>78000000</v>
       </c>
       <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr">
@@ -4406,16 +4400,16 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G27</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G30</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>chr18</t>
+          <t>chr14</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>58400000</v>
+        <v>43200000</v>
       </c>
       <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr">
@@ -4433,16 +4427,16 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G27</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G30</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>chr2</t>
+          <t>chr14</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>29400000</v>
+        <v>66800000</v>
       </c>
       <c r="E148" t="inlineStr"/>
       <c r="F148" t="inlineStr">
@@ -4460,16 +4454,16 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G27</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G30</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>chr20</t>
+          <t>chr2</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>25000000</v>
+        <v>52000000</v>
       </c>
       <c r="E149" t="inlineStr"/>
       <c r="F149" t="inlineStr">
@@ -4487,26 +4481,24 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G27</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G30</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>chr20</t>
+          <t>chr3</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>31800000</v>
+        <v>151400000</v>
       </c>
       <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Translocation</t>
-        </is>
-      </c>
-      <c r="G150" t="n">
-        <v>6.25</v>
-      </c>
+          <t>SCE</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -4516,16 +4508,16 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G27</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G30</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>chr3</t>
+          <t>chr4</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>66800000</v>
+        <v>182800000</v>
       </c>
       <c r="E151" t="inlineStr"/>
       <c r="F151" t="inlineStr">
@@ -4543,16 +4535,16 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G28</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G30</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>chr1</t>
+          <t>chr6</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>30800000</v>
+        <v>56600000</v>
       </c>
       <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr">
@@ -4570,16 +4562,16 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G28</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G32</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>chr10</t>
+          <t>chr11</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>16800000</v>
+        <v>13800000</v>
       </c>
       <c r="E153" t="inlineStr"/>
       <c r="F153" t="inlineStr">
@@ -4597,24 +4589,26 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G28</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G32</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>chr11</t>
+          <t>chr13</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>63000000</v>
+        <v>18400000</v>
       </c>
       <c r="E154" t="inlineStr"/>
       <c r="F154" t="inlineStr">
         <is>
-          <t>SCE</t>
-        </is>
-      </c>
-      <c r="G154" t="inlineStr"/>
+          <t>Translocation</t>
+        </is>
+      </c>
+      <c r="G154" t="n">
+        <v>9.380000000000001</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -4624,16 +4618,16 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G28</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G32</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>chr12</t>
+          <t>chr15</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>99600000</v>
+        <v>40800000</v>
       </c>
       <c r="E155" t="inlineStr"/>
       <c r="F155" t="inlineStr">
@@ -4651,16 +4645,16 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G28</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G32</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>chr21</t>
+          <t>chr16</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>25800000</v>
+        <v>72000000</v>
       </c>
       <c r="E156" t="inlineStr"/>
       <c r="F156" t="inlineStr">
@@ -4678,16 +4672,16 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G28</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G32</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>chr22</t>
+          <t>chr18</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>42200000</v>
+        <v>40400000</v>
       </c>
       <c r="E157" t="inlineStr"/>
       <c r="F157" t="inlineStr">
@@ -4705,24 +4699,26 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G28</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G32</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>chr4</t>
+          <t>chr20</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>41000000</v>
+        <v>31200000</v>
       </c>
       <c r="E158" t="inlineStr"/>
       <c r="F158" t="inlineStr">
         <is>
-          <t>SCE</t>
-        </is>
-      </c>
-      <c r="G158" t="inlineStr"/>
+          <t>Translocation</t>
+        </is>
+      </c>
+      <c r="G158" t="n">
+        <v>9.380000000000001</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -4732,16 +4728,16 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G28</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G32</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>chr7</t>
+          <t>chr3</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>5600000</v>
+        <v>56400000</v>
       </c>
       <c r="E159" t="inlineStr"/>
       <c r="F159" t="inlineStr">
@@ -4759,16 +4755,16 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G28</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G32</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>chr7</t>
+          <t>chr3</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>19800000</v>
+        <v>151000000</v>
       </c>
       <c r="E160" t="inlineStr"/>
       <c r="F160" t="inlineStr">
@@ -4786,24 +4782,26 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G30</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G32</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>chr1</t>
+          <t>chr5</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>219400000</v>
+        <v>71400000</v>
       </c>
       <c r="E161" t="inlineStr"/>
       <c r="F161" t="inlineStr">
         <is>
-          <t>SCE</t>
-        </is>
-      </c>
-      <c r="G161" t="inlineStr"/>
+          <t>Translocation</t>
+        </is>
+      </c>
+      <c r="G161" t="n">
+        <v>6.25</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -4813,24 +4811,26 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G30</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G32</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>chr12</t>
+          <t>chr9</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>78000000</v>
+        <v>69400000</v>
       </c>
       <c r="E162" t="inlineStr"/>
       <c r="F162" t="inlineStr">
         <is>
-          <t>SCE</t>
-        </is>
-      </c>
-      <c r="G162" t="inlineStr"/>
+          <t>Translocation</t>
+        </is>
+      </c>
+      <c r="G162" t="n">
+        <v>6.25</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -4840,16 +4840,16 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G30</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G37</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>chr14</t>
+          <t>chr12</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>49800000</v>
+        <v>95600000</v>
       </c>
       <c r="E163" t="inlineStr"/>
       <c r="F163" t="inlineStr">
@@ -4867,24 +4867,26 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G30</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G37</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>chr14</t>
+          <t>chr16</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>66800000</v>
+        <v>47600000</v>
       </c>
       <c r="E164" t="inlineStr"/>
       <c r="F164" t="inlineStr">
         <is>
-          <t>SCE</t>
-        </is>
-      </c>
-      <c r="G164" t="inlineStr"/>
+          <t>Translocation</t>
+        </is>
+      </c>
+      <c r="G164" t="n">
+        <v>9.380000000000001</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -4894,16 +4896,16 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G30</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G37</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>chr16</t>
+          <t>chr5</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>12600000</v>
+        <v>25000000</v>
       </c>
       <c r="E165" t="inlineStr"/>
       <c r="F165" t="inlineStr">
@@ -4921,16 +4923,16 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G30</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G37</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>chr2</t>
+          <t>chr8</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>52000000</v>
+        <v>22000000</v>
       </c>
       <c r="E166" t="inlineStr"/>
       <c r="F166" t="inlineStr">
@@ -4948,16 +4950,16 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G30</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G37</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>chr3</t>
+          <t>chr9</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>151400000</v>
+        <v>6000000</v>
       </c>
       <c r="E167" t="inlineStr"/>
       <c r="F167" t="inlineStr">
@@ -4975,16 +4977,16 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G30</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G37</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>chr4</t>
+          <t>chrX</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>182800000</v>
+        <v>97600000</v>
       </c>
       <c r="E168" t="inlineStr"/>
       <c r="F168" t="inlineStr">
@@ -5002,16 +5004,16 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G30</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G38</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>chr6</t>
+          <t>chr13</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>56600000</v>
+        <v>72200000</v>
       </c>
       <c r="E169" t="inlineStr"/>
       <c r="F169" t="inlineStr">
@@ -5029,16 +5031,16 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G32</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G38</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>chr11</t>
+          <t>chr13</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>13800000</v>
+        <v>81400000</v>
       </c>
       <c r="E170" t="inlineStr"/>
       <c r="F170" t="inlineStr">
@@ -5056,26 +5058,24 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G32</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G38</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>chr13</t>
+          <t>chr2</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>18400000</v>
+        <v>19600000</v>
       </c>
       <c r="E171" t="inlineStr"/>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Translocation</t>
-        </is>
-      </c>
-      <c r="G171" t="n">
-        <v>9.380000000000001</v>
-      </c>
+          <t>SCE</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -5085,16 +5085,16 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G32</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G38</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>chr15</t>
+          <t>chr3</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>40800000</v>
+        <v>46200000</v>
       </c>
       <c r="E172" t="inlineStr"/>
       <c r="F172" t="inlineStr">
@@ -5112,16 +5112,16 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G32</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G38</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>chr16</t>
+          <t>chr6</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>72000000</v>
+        <v>162800000</v>
       </c>
       <c r="E173" t="inlineStr"/>
       <c r="F173" t="inlineStr">
@@ -5139,16 +5139,16 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G32</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G38</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>chr18</t>
+          <t>chr7</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>40400000</v>
+        <v>86800000</v>
       </c>
       <c r="E174" t="inlineStr"/>
       <c r="F174" t="inlineStr">
@@ -5166,26 +5166,24 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G32</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G38</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>chr20</t>
+          <t>chr8</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>31200000</v>
+        <v>117800000</v>
       </c>
       <c r="E175" t="inlineStr"/>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Translocation</t>
-        </is>
-      </c>
-      <c r="G175" t="n">
-        <v>9.380000000000001</v>
-      </c>
+          <t>SCE</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -5195,16 +5193,16 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G32</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G38</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>chr3</t>
+          <t>chr8</t>
         </is>
       </c>
       <c r="D176" t="n">
-        <v>56400000</v>
+        <v>120600000</v>
       </c>
       <c r="E176" t="inlineStr"/>
       <c r="F176" t="inlineStr">
@@ -5222,16 +5220,16 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G32</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G38</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>chr3</t>
+          <t>chrX</t>
         </is>
       </c>
       <c r="D177" t="n">
-        <v>151000000</v>
+        <v>149600000</v>
       </c>
       <c r="E177" t="inlineStr"/>
       <c r="F177" t="inlineStr">
@@ -5249,26 +5247,24 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G32</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G39</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>chr5</t>
+          <t>chr10</t>
         </is>
       </c>
       <c r="D178" t="n">
-        <v>71400000</v>
+        <v>86200000</v>
       </c>
       <c r="E178" t="inlineStr"/>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Translocation</t>
-        </is>
-      </c>
-      <c r="G178" t="n">
-        <v>6.25</v>
-      </c>
+          <t>SCE</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -5278,26 +5274,24 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G32</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G39</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>chr9</t>
+          <t>chr15</t>
         </is>
       </c>
       <c r="D179" t="n">
-        <v>69400000</v>
+        <v>36000000</v>
       </c>
       <c r="E179" t="inlineStr"/>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Translocation</t>
-        </is>
-      </c>
-      <c r="G179" t="n">
-        <v>6.25</v>
-      </c>
+          <t>SCE</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -5307,16 +5301,16 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G37</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G39</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>chr12</t>
+          <t>chr4</t>
         </is>
       </c>
       <c r="D180" t="n">
-        <v>95600000</v>
+        <v>55800000</v>
       </c>
       <c r="E180" t="inlineStr"/>
       <c r="F180" t="inlineStr">
@@ -5334,26 +5328,24 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G37</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G39</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>chr16</t>
+          <t>chr9</t>
         </is>
       </c>
       <c r="D181" t="n">
-        <v>47600000</v>
+        <v>11400000</v>
       </c>
       <c r="E181" t="inlineStr"/>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Translocation</t>
-        </is>
-      </c>
-      <c r="G181" t="n">
-        <v>9.380000000000001</v>
-      </c>
+          <t>SCE</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -5363,16 +5355,16 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G37</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G49</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>chr5</t>
+          <t>chr1</t>
         </is>
       </c>
       <c r="D182" t="n">
-        <v>25000000</v>
+        <v>98800000</v>
       </c>
       <c r="E182" t="inlineStr"/>
       <c r="F182" t="inlineStr">
@@ -5390,16 +5382,16 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G37</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G49</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>chr8</t>
+          <t>chr1</t>
         </is>
       </c>
       <c r="D183" t="n">
-        <v>22000000</v>
+        <v>104200000</v>
       </c>
       <c r="E183" t="inlineStr"/>
       <c r="F183" t="inlineStr">
@@ -5417,16 +5409,16 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G37</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G49</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>chr9</t>
+          <t>chr1</t>
         </is>
       </c>
       <c r="D184" t="n">
-        <v>6000000</v>
+        <v>107800000</v>
       </c>
       <c r="E184" t="inlineStr"/>
       <c r="F184" t="inlineStr">
@@ -5444,16 +5436,16 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G37</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G49</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>chrX</t>
+          <t>chr12</t>
         </is>
       </c>
       <c r="D185" t="n">
-        <v>97600000</v>
+        <v>13600000</v>
       </c>
       <c r="E185" t="inlineStr"/>
       <c r="F185" t="inlineStr">
@@ -5471,16 +5463,16 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G38</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G49</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>chr11</t>
+          <t>chr15</t>
         </is>
       </c>
       <c r="D186" t="n">
-        <v>39200000</v>
+        <v>27800000</v>
       </c>
       <c r="E186" t="inlineStr"/>
       <c r="F186" t="inlineStr">
@@ -5498,16 +5490,16 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G38</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G49</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>chr11</t>
+          <t>chr15</t>
         </is>
       </c>
       <c r="D187" t="n">
-        <v>43000000</v>
+        <v>70600000</v>
       </c>
       <c r="E187" t="inlineStr"/>
       <c r="F187" t="inlineStr">
@@ -5525,16 +5517,16 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G38</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G49</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>chr13</t>
+          <t>chr16</t>
         </is>
       </c>
       <c r="D188" t="n">
-        <v>72200000</v>
+        <v>59800000</v>
       </c>
       <c r="E188" t="inlineStr"/>
       <c r="F188" t="inlineStr">
@@ -5552,16 +5544,16 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G38</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G49</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>chr13</t>
+          <t>chr16</t>
         </is>
       </c>
       <c r="D189" t="n">
-        <v>81400000</v>
+        <v>65800000</v>
       </c>
       <c r="E189" t="inlineStr"/>
       <c r="F189" t="inlineStr">
@@ -5579,26 +5571,24 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G38</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G49</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>chr16</t>
+          <t>chr18</t>
         </is>
       </c>
       <c r="D190" t="n">
-        <v>59800000</v>
+        <v>31400000</v>
       </c>
       <c r="E190" t="inlineStr"/>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Translocation</t>
-        </is>
-      </c>
-      <c r="G190" t="n">
-        <v>6.25</v>
-      </c>
+          <t>SCE</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -5608,16 +5598,16 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G38</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G49</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>chr16</t>
+          <t>chr19</t>
         </is>
       </c>
       <c r="D191" t="n">
-        <v>64800000</v>
+        <v>19400000</v>
       </c>
       <c r="E191" t="inlineStr"/>
       <c r="F191" t="inlineStr">
@@ -5635,16 +5625,16 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G38</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G49</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>chr2</t>
+          <t>chr22</t>
         </is>
       </c>
       <c r="D192" t="n">
-        <v>19600000</v>
+        <v>24400000</v>
       </c>
       <c r="E192" t="inlineStr"/>
       <c r="F192" t="inlineStr">
@@ -5662,7 +5652,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G38</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G49</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -5671,7 +5661,7 @@
         </is>
       </c>
       <c r="D193" t="n">
-        <v>46200000</v>
+        <v>147200000</v>
       </c>
       <c r="E193" t="inlineStr"/>
       <c r="F193" t="inlineStr">
@@ -5689,16 +5679,16 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G38</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G49</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>chr5</t>
+          <t>chr4</t>
         </is>
       </c>
       <c r="D194" t="n">
-        <v>20400000</v>
+        <v>107000000</v>
       </c>
       <c r="E194" t="inlineStr"/>
       <c r="F194" t="inlineStr">
@@ -5716,26 +5706,24 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G38</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G49</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>chr5</t>
+          <t>chr7</t>
         </is>
       </c>
       <c r="D195" t="n">
-        <v>26600000</v>
+        <v>130400000</v>
       </c>
       <c r="E195" t="inlineStr"/>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Translocation</t>
-        </is>
-      </c>
-      <c r="G195" t="n">
-        <v>6.25</v>
-      </c>
+          <t>SCE</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -5745,26 +5733,24 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G38</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G49</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>chr6</t>
+          <t>chr8</t>
         </is>
       </c>
       <c r="D196" t="n">
-        <v>90800000</v>
+        <v>27600000</v>
       </c>
       <c r="E196" t="inlineStr"/>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Translocation</t>
-        </is>
-      </c>
-      <c r="G196" t="n">
-        <v>9.380000000000001</v>
-      </c>
+          <t>SCE</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -5774,16 +5760,16 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G38</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G51</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>chr6</t>
+          <t>chr1</t>
         </is>
       </c>
       <c r="D197" t="n">
-        <v>95400000</v>
+        <v>76800000</v>
       </c>
       <c r="E197" t="inlineStr"/>
       <c r="F197" t="inlineStr">
@@ -5801,16 +5787,16 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G38</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G51</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>chr6</t>
+          <t>chr11</t>
         </is>
       </c>
       <c r="D198" t="n">
-        <v>162800000</v>
+        <v>57000000</v>
       </c>
       <c r="E198" t="inlineStr"/>
       <c r="F198" t="inlineStr">
@@ -5828,16 +5814,16 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G38</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G51</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>chr7</t>
+          <t>chr16</t>
         </is>
       </c>
       <c r="D199" t="n">
-        <v>86800000</v>
+        <v>11000000</v>
       </c>
       <c r="E199" t="inlineStr"/>
       <c r="F199" t="inlineStr">
@@ -5855,16 +5841,16 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G38</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G51</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>chr8</t>
+          <t>chr4</t>
         </is>
       </c>
       <c r="D200" t="n">
-        <v>117800000</v>
+        <v>149000000</v>
       </c>
       <c r="E200" t="inlineStr"/>
       <c r="F200" t="inlineStr">
@@ -5882,16 +5868,16 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G38</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G51</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>chr8</t>
+          <t>chr4</t>
         </is>
       </c>
       <c r="D201" t="n">
-        <v>120600000</v>
+        <v>158600000</v>
       </c>
       <c r="E201" t="inlineStr"/>
       <c r="F201" t="inlineStr">
@@ -5909,16 +5895,16 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G38</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G51</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>chrX</t>
+          <t>chr6</t>
         </is>
       </c>
       <c r="D202" t="n">
-        <v>149600000</v>
+        <v>155000000</v>
       </c>
       <c r="E202" t="inlineStr"/>
       <c r="F202" t="inlineStr">
@@ -5936,16 +5922,16 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G39</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G51</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>chr10</t>
+          <t>chr8</t>
         </is>
       </c>
       <c r="D203" t="n">
-        <v>86200000</v>
+        <v>98400000</v>
       </c>
       <c r="E203" t="inlineStr"/>
       <c r="F203" t="inlineStr">
@@ -5963,24 +5949,28 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G39</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G52</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>chr15</t>
+          <t>chr1</t>
         </is>
       </c>
       <c r="D204" t="n">
-        <v>36000000</v>
-      </c>
-      <c r="E204" t="inlineStr"/>
+        <v>147600000</v>
+      </c>
+      <c r="E204" t="n">
+        <v>149600000</v>
+      </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>SCE</t>
-        </is>
-      </c>
-      <c r="G204" t="inlineStr"/>
+          <t>Inversion</t>
+        </is>
+      </c>
+      <c r="G204" t="n">
+        <v>6.25</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -5990,26 +5980,24 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G39</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G52</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>chr20</t>
+          <t>chr10</t>
         </is>
       </c>
       <c r="D205" t="n">
-        <v>31400000</v>
+        <v>37800000</v>
       </c>
       <c r="E205" t="inlineStr"/>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Translocation</t>
-        </is>
-      </c>
-      <c r="G205" t="n">
-        <v>6.25</v>
-      </c>
+          <t>SCE</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -6019,16 +6007,16 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G39</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G52</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>chr20</t>
+          <t>chr12</t>
         </is>
       </c>
       <c r="D206" t="n">
-        <v>32400000</v>
+        <v>73600000</v>
       </c>
       <c r="E206" t="inlineStr"/>
       <c r="F206" t="inlineStr">
@@ -6046,16 +6034,16 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G39</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G52</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>chr4</t>
+          <t>chr16</t>
         </is>
       </c>
       <c r="D207" t="n">
-        <v>55800000</v>
+        <v>26000000</v>
       </c>
       <c r="E207" t="inlineStr"/>
       <c r="F207" t="inlineStr">
@@ -6073,16 +6061,16 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G39</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G52</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>chr9</t>
+          <t>chr2</t>
         </is>
       </c>
       <c r="D208" t="n">
-        <v>11400000</v>
+        <v>21400000</v>
       </c>
       <c r="E208" t="inlineStr"/>
       <c r="F208" t="inlineStr">
@@ -6100,16 +6088,16 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G49</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G52</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>chr1</t>
+          <t>chr20</t>
         </is>
       </c>
       <c r="D209" t="n">
-        <v>98800000</v>
+        <v>38800000</v>
       </c>
       <c r="E209" t="inlineStr"/>
       <c r="F209" t="inlineStr">
@@ -6127,16 +6115,16 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G49</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G52</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>chr1</t>
+          <t>chr3</t>
         </is>
       </c>
       <c r="D210" t="n">
-        <v>104200000</v>
+        <v>5800000</v>
       </c>
       <c r="E210" t="inlineStr"/>
       <c r="F210" t="inlineStr">
@@ -6154,16 +6142,16 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G49</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G52</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>chr1</t>
+          <t>chr5</t>
         </is>
       </c>
       <c r="D211" t="n">
-        <v>107800000</v>
+        <v>26400000</v>
       </c>
       <c r="E211" t="inlineStr"/>
       <c r="F211" t="inlineStr">
@@ -6181,16 +6169,16 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G49</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G52</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>chr12</t>
+          <t>chr5</t>
         </is>
       </c>
       <c r="D212" t="n">
-        <v>13600000</v>
+        <v>128800000</v>
       </c>
       <c r="E212" t="inlineStr"/>
       <c r="F212" t="inlineStr">
@@ -6208,24 +6196,26 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G49</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G52</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>chr15</t>
+          <t>chr9</t>
         </is>
       </c>
       <c r="D213" t="n">
-        <v>27800000</v>
+        <v>69400000</v>
       </c>
       <c r="E213" t="inlineStr"/>
       <c r="F213" t="inlineStr">
         <is>
-          <t>SCE</t>
-        </is>
-      </c>
-      <c r="G213" t="inlineStr"/>
+          <t>Translocation</t>
+        </is>
+      </c>
+      <c r="G213" t="n">
+        <v>6.25</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -6235,16 +6225,16 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G49</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G52</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>chr15</t>
+          <t>chr9</t>
         </is>
       </c>
       <c r="D214" t="n">
-        <v>70600000</v>
+        <v>103000000</v>
       </c>
       <c r="E214" t="inlineStr"/>
       <c r="F214" t="inlineStr">
@@ -6262,21 +6252,23 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G49</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G57</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>chr16</t>
+          <t>chr1</t>
         </is>
       </c>
       <c r="D215" t="n">
-        <v>59800000</v>
-      </c>
-      <c r="E215" t="inlineStr"/>
+        <v>147600000</v>
+      </c>
+      <c r="E215" t="n">
+        <v>149600000</v>
+      </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Translocation</t>
+          <t>Inversion</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -6291,16 +6283,16 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G49</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G57</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>chr16</t>
+          <t>chr10</t>
         </is>
       </c>
       <c r="D216" t="n">
-        <v>65800000</v>
+        <v>35400000</v>
       </c>
       <c r="E216" t="inlineStr"/>
       <c r="F216" t="inlineStr">
@@ -6318,16 +6310,16 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G49</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G57</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>chr18</t>
+          <t>chr14</t>
         </is>
       </c>
       <c r="D217" t="n">
-        <v>31400000</v>
+        <v>86000000</v>
       </c>
       <c r="E217" t="inlineStr"/>
       <c r="F217" t="inlineStr">
@@ -6345,16 +6337,16 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G49</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G57</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>chr19</t>
+          <t>chr16</t>
         </is>
       </c>
       <c r="D218" t="n">
-        <v>19400000</v>
+        <v>78200000</v>
       </c>
       <c r="E218" t="inlineStr"/>
       <c r="F218" t="inlineStr">
@@ -6372,16 +6364,16 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G49</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G57</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>chr22</t>
+          <t>chr17</t>
         </is>
       </c>
       <c r="D219" t="n">
-        <v>24400000</v>
+        <v>41600000</v>
       </c>
       <c r="E219" t="inlineStr"/>
       <c r="F219" t="inlineStr">
@@ -6399,16 +6391,16 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G49</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G57</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>chr3</t>
+          <t>chr19</t>
         </is>
       </c>
       <c r="D220" t="n">
-        <v>147200000</v>
+        <v>8200000</v>
       </c>
       <c r="E220" t="inlineStr"/>
       <c r="F220" t="inlineStr">
@@ -6426,16 +6418,16 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G49</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G57</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>chr4</t>
+          <t>chr2</t>
         </is>
       </c>
       <c r="D221" t="n">
-        <v>107000000</v>
+        <v>82400000</v>
       </c>
       <c r="E221" t="inlineStr"/>
       <c r="F221" t="inlineStr">
@@ -6453,16 +6445,16 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G49</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G57</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>chr5</t>
+          <t>chr2</t>
         </is>
       </c>
       <c r="D222" t="n">
-        <v>21400000</v>
+        <v>117800000</v>
       </c>
       <c r="E222" t="inlineStr"/>
       <c r="F222" t="inlineStr">
@@ -6480,16 +6472,16 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G49</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G57</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>chr5</t>
+          <t>chr4</t>
         </is>
       </c>
       <c r="D223" t="n">
-        <v>30800000</v>
+        <v>143200000</v>
       </c>
       <c r="E223" t="inlineStr"/>
       <c r="F223" t="inlineStr">
@@ -6507,26 +6499,24 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G49</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G57</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>chr6</t>
+          <t>chr5</t>
         </is>
       </c>
       <c r="D224" t="n">
-        <v>90800000</v>
+        <v>117000000</v>
       </c>
       <c r="E224" t="inlineStr"/>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Translocation</t>
-        </is>
-      </c>
-      <c r="G224" t="n">
-        <v>9.380000000000001</v>
-      </c>
+          <t>SCE</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -6536,7 +6526,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G49</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G57</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -6545,7 +6535,7 @@
         </is>
       </c>
       <c r="D225" t="n">
-        <v>96800000</v>
+        <v>138600000</v>
       </c>
       <c r="E225" t="inlineStr"/>
       <c r="F225" t="inlineStr">
@@ -6563,16 +6553,16 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G49</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G57</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>chr7</t>
+          <t>chr8</t>
         </is>
       </c>
       <c r="D226" t="n">
-        <v>130400000</v>
+        <v>64200000</v>
       </c>
       <c r="E226" t="inlineStr"/>
       <c r="F226" t="inlineStr">
@@ -6590,16 +6580,16 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G49</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G57</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>chr8</t>
+          <t>chr9</t>
         </is>
       </c>
       <c r="D227" t="n">
-        <v>27600000</v>
+        <v>94600000</v>
       </c>
       <c r="E227" t="inlineStr"/>
       <c r="F227" t="inlineStr">
@@ -6617,16 +6607,16 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G51</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G57</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>chr1</t>
+          <t>chr9</t>
         </is>
       </c>
       <c r="D228" t="n">
-        <v>76800000</v>
+        <v>128000000</v>
       </c>
       <c r="E228" t="inlineStr"/>
       <c r="F228" t="inlineStr">
@@ -6644,16 +6634,16 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G51</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G57</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>chr11</t>
+          <t>chrX</t>
         </is>
       </c>
       <c r="D229" t="n">
-        <v>57000000</v>
+        <v>90400000</v>
       </c>
       <c r="E229" t="inlineStr"/>
       <c r="F229" t="inlineStr">
@@ -6671,16 +6661,16 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G51</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G61</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>chr16</t>
+          <t>chr10</t>
         </is>
       </c>
       <c r="D230" t="n">
-        <v>11000000</v>
+        <v>5800000</v>
       </c>
       <c r="E230" t="inlineStr"/>
       <c r="F230" t="inlineStr">
@@ -6698,16 +6688,16 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G51</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G61</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>chr4</t>
+          <t>chr11</t>
         </is>
       </c>
       <c r="D231" t="n">
-        <v>149000000</v>
+        <v>58000000</v>
       </c>
       <c r="E231" t="inlineStr"/>
       <c r="F231" t="inlineStr">
@@ -6725,16 +6715,16 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G51</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G61</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>chr4</t>
+          <t>chr12</t>
         </is>
       </c>
       <c r="D232" t="n">
-        <v>158600000</v>
+        <v>42800000</v>
       </c>
       <c r="E232" t="inlineStr"/>
       <c r="F232" t="inlineStr">
@@ -6752,16 +6742,16 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G51</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G61</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>chr6</t>
+          <t>chr14</t>
         </is>
       </c>
       <c r="D233" t="n">
-        <v>155000000</v>
+        <v>54200000</v>
       </c>
       <c r="E233" t="inlineStr"/>
       <c r="F233" t="inlineStr">
@@ -6779,24 +6769,26 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G51</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G61</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>chr8</t>
+          <t>chr16</t>
         </is>
       </c>
       <c r="D234" t="n">
-        <v>98400000</v>
+        <v>47600000</v>
       </c>
       <c r="E234" t="inlineStr"/>
       <c r="F234" t="inlineStr">
         <is>
-          <t>SCE</t>
-        </is>
-      </c>
-      <c r="G234" t="inlineStr"/>
+          <t>Translocation</t>
+        </is>
+      </c>
+      <c r="G234" t="n">
+        <v>9.380000000000001</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -6806,28 +6798,24 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G52</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G61</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>chr1</t>
+          <t>chr19</t>
         </is>
       </c>
       <c r="D235" t="n">
-        <v>147600000</v>
-      </c>
-      <c r="E235" t="n">
-        <v>149600000</v>
-      </c>
+        <v>28200000</v>
+      </c>
+      <c r="E235" t="inlineStr"/>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Inversion</t>
-        </is>
-      </c>
-      <c r="G235" t="n">
-        <v>6.25</v>
-      </c>
+          <t>SCE</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -6837,16 +6825,16 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G52</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G61</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>chr10</t>
+          <t>chr19</t>
         </is>
       </c>
       <c r="D236" t="n">
-        <v>37800000</v>
+        <v>39800000</v>
       </c>
       <c r="E236" t="inlineStr"/>
       <c r="F236" t="inlineStr">
@@ -6864,16 +6852,16 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G52</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G61</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>chr12</t>
+          <t>chr22</t>
         </is>
       </c>
       <c r="D237" t="n">
-        <v>73600000</v>
+        <v>27000000</v>
       </c>
       <c r="E237" t="inlineStr"/>
       <c r="F237" t="inlineStr">
@@ -6891,16 +6879,16 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G52</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G61</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>chr16</t>
+          <t>chr3</t>
         </is>
       </c>
       <c r="D238" t="n">
-        <v>26000000</v>
+        <v>176400000</v>
       </c>
       <c r="E238" t="inlineStr"/>
       <c r="F238" t="inlineStr">
@@ -6918,16 +6906,16 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G52</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G61</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>chr2</t>
+          <t>chr5</t>
         </is>
       </c>
       <c r="D239" t="n">
-        <v>21400000</v>
+        <v>83200000</v>
       </c>
       <c r="E239" t="inlineStr"/>
       <c r="F239" t="inlineStr">
@@ -6945,16 +6933,16 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G52</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G61</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>chr20</t>
+          <t>chr7</t>
         </is>
       </c>
       <c r="D240" t="n">
-        <v>38800000</v>
+        <v>12400000</v>
       </c>
       <c r="E240" t="inlineStr"/>
       <c r="F240" t="inlineStr">
@@ -6972,16 +6960,16 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G52</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G61</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>chr3</t>
+          <t>chr8</t>
         </is>
       </c>
       <c r="D241" t="n">
-        <v>5800000</v>
+        <v>44800000</v>
       </c>
       <c r="E241" t="inlineStr"/>
       <c r="F241" t="inlineStr">
@@ -6999,16 +6987,16 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G52</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G61</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>chr5</t>
+          <t>chrX</t>
         </is>
       </c>
       <c r="D242" t="n">
-        <v>26400000</v>
+        <v>154200000</v>
       </c>
       <c r="E242" t="inlineStr"/>
       <c r="F242" t="inlineStr">
@@ -7026,16 +7014,16 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G52</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G63</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>chr5</t>
+          <t>chr1</t>
         </is>
       </c>
       <c r="D243" t="n">
-        <v>128800000</v>
+        <v>212600000</v>
       </c>
       <c r="E243" t="inlineStr"/>
       <c r="F243" t="inlineStr">
@@ -7053,26 +7041,24 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G52</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G63</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>chr9</t>
+          <t>chr10</t>
         </is>
       </c>
       <c r="D244" t="n">
-        <v>69400000</v>
+        <v>28400000</v>
       </c>
       <c r="E244" t="inlineStr"/>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Translocation</t>
-        </is>
-      </c>
-      <c r="G244" t="n">
-        <v>6.25</v>
-      </c>
+          <t>SCE</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -7082,16 +7068,16 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G52</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G63</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>chr9</t>
+          <t>chr10</t>
         </is>
       </c>
       <c r="D245" t="n">
-        <v>103000000</v>
+        <v>128000000</v>
       </c>
       <c r="E245" t="inlineStr"/>
       <c r="F245" t="inlineStr">
@@ -7109,28 +7095,24 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G57</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G63</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>chr1</t>
+          <t>chr11</t>
         </is>
       </c>
       <c r="D246" t="n">
-        <v>147600000</v>
-      </c>
-      <c r="E246" t="n">
-        <v>149600000</v>
-      </c>
+        <v>102600000</v>
+      </c>
+      <c r="E246" t="inlineStr"/>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Inversion</t>
-        </is>
-      </c>
-      <c r="G246" t="n">
-        <v>6.25</v>
-      </c>
+          <t>SCE</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -7140,16 +7122,16 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G57</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G63</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>chr10</t>
+          <t>chr14</t>
         </is>
       </c>
       <c r="D247" t="n">
-        <v>35400000</v>
+        <v>33400000</v>
       </c>
       <c r="E247" t="inlineStr"/>
       <c r="F247" t="inlineStr">
@@ -7167,16 +7149,16 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G57</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G63</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>chr14</t>
+          <t>chr16</t>
         </is>
       </c>
       <c r="D248" t="n">
-        <v>86000000</v>
+        <v>83800000</v>
       </c>
       <c r="E248" t="inlineStr"/>
       <c r="F248" t="inlineStr">
@@ -7194,16 +7176,16 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G57</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G63</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>chr16</t>
+          <t>chr17</t>
         </is>
       </c>
       <c r="D249" t="n">
-        <v>78200000</v>
+        <v>65600000</v>
       </c>
       <c r="E249" t="inlineStr"/>
       <c r="F249" t="inlineStr">
@@ -7221,16 +7203,16 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G57</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G64</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>chr17</t>
+          <t>chr1</t>
         </is>
       </c>
       <c r="D250" t="n">
-        <v>41600000</v>
+        <v>231800000</v>
       </c>
       <c r="E250" t="inlineStr"/>
       <c r="F250" t="inlineStr">
@@ -7248,16 +7230,16 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G57</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G64</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>chr19</t>
+          <t>chr10</t>
         </is>
       </c>
       <c r="D251" t="n">
-        <v>8200000</v>
+        <v>112800000</v>
       </c>
       <c r="E251" t="inlineStr"/>
       <c r="F251" t="inlineStr">
@@ -7275,26 +7257,24 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G57</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G64</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>chr2</t>
+          <t>chr11</t>
         </is>
       </c>
       <c r="D252" t="n">
-        <v>82400000</v>
+        <v>55600000</v>
       </c>
       <c r="E252" t="inlineStr"/>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Translocation</t>
-        </is>
-      </c>
-      <c r="G252" t="n">
-        <v>6.25</v>
-      </c>
+          <t>SCE</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -7304,16 +7284,16 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G57</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G64</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>chr2</t>
+          <t>chr12</t>
         </is>
       </c>
       <c r="D253" t="n">
-        <v>117800000</v>
+        <v>111000000</v>
       </c>
       <c r="E253" t="inlineStr"/>
       <c r="F253" t="inlineStr">
@@ -7331,16 +7311,16 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G57</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G64</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>chr4</t>
+          <t>chr16</t>
         </is>
       </c>
       <c r="D254" t="n">
-        <v>143200000</v>
+        <v>24000000</v>
       </c>
       <c r="E254" t="inlineStr"/>
       <c r="F254" t="inlineStr">
@@ -7358,16 +7338,16 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G57</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G64</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>chr5</t>
+          <t>chr2</t>
         </is>
       </c>
       <c r="D255" t="n">
-        <v>117000000</v>
+        <v>138200000</v>
       </c>
       <c r="E255" t="inlineStr"/>
       <c r="F255" t="inlineStr">
@@ -7385,16 +7365,16 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G57</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G64</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>chr6</t>
+          <t>chr5</t>
         </is>
       </c>
       <c r="D256" t="n">
-        <v>138600000</v>
+        <v>98200000</v>
       </c>
       <c r="E256" t="inlineStr"/>
       <c r="F256" t="inlineStr">
@@ -7412,16 +7392,16 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G57</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G64</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>chr8</t>
+          <t>chr6</t>
         </is>
       </c>
       <c r="D257" t="n">
-        <v>64200000</v>
+        <v>64000000</v>
       </c>
       <c r="E257" t="inlineStr"/>
       <c r="F257" t="inlineStr">
@@ -7439,16 +7419,16 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G57</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G64</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>chr9</t>
+          <t>chrX</t>
         </is>
       </c>
       <c r="D258" t="n">
-        <v>94600000</v>
+        <v>37400000</v>
       </c>
       <c r="E258" t="inlineStr"/>
       <c r="F258" t="inlineStr">
@@ -7466,16 +7446,16 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G57</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G74</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>chr9</t>
+          <t>chr1</t>
         </is>
       </c>
       <c r="D259" t="n">
-        <v>128000000</v>
+        <v>242400000</v>
       </c>
       <c r="E259" t="inlineStr"/>
       <c r="F259" t="inlineStr">
@@ -7493,16 +7473,16 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G57</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G74</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>chrX</t>
+          <t>chr10</t>
         </is>
       </c>
       <c r="D260" t="n">
-        <v>90400000</v>
+        <v>97600000</v>
       </c>
       <c r="E260" t="inlineStr"/>
       <c r="F260" t="inlineStr">
@@ -7520,16 +7500,16 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G61</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G74</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>chr10</t>
+          <t>chr12</t>
         </is>
       </c>
       <c r="D261" t="n">
-        <v>5800000</v>
+        <v>120600000</v>
       </c>
       <c r="E261" t="inlineStr"/>
       <c r="F261" t="inlineStr">
@@ -7547,24 +7527,26 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G61</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G74</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>chr11</t>
+          <t>chr13</t>
         </is>
       </c>
       <c r="D262" t="n">
-        <v>58000000</v>
+        <v>18400000</v>
       </c>
       <c r="E262" t="inlineStr"/>
       <c r="F262" t="inlineStr">
         <is>
-          <t>SCE</t>
-        </is>
-      </c>
-      <c r="G262" t="inlineStr"/>
+          <t>Translocation</t>
+        </is>
+      </c>
+      <c r="G262" t="n">
+        <v>9.380000000000001</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -7574,16 +7556,16 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G61</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G74</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>chr12</t>
+          <t>chr13</t>
         </is>
       </c>
       <c r="D263" t="n">
-        <v>42800000</v>
+        <v>82600000</v>
       </c>
       <c r="E263" t="inlineStr"/>
       <c r="F263" t="inlineStr">
@@ -7601,16 +7583,16 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G61</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G74</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>chr14</t>
+          <t>chr13</t>
         </is>
       </c>
       <c r="D264" t="n">
-        <v>54200000</v>
+        <v>104800000</v>
       </c>
       <c r="E264" t="inlineStr"/>
       <c r="F264" t="inlineStr">
@@ -7628,26 +7610,24 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G61</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G74</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>chr16</t>
+          <t>chr2</t>
         </is>
       </c>
       <c r="D265" t="n">
-        <v>47600000</v>
+        <v>82000000</v>
       </c>
       <c r="E265" t="inlineStr"/>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Translocation</t>
-        </is>
-      </c>
-      <c r="G265" t="n">
-        <v>9.380000000000001</v>
-      </c>
+          <t>SCE</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -7657,16 +7637,16 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G61</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G74</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>chr19</t>
+          <t>chr22</t>
         </is>
       </c>
       <c r="D266" t="n">
-        <v>28200000</v>
+        <v>33600000</v>
       </c>
       <c r="E266" t="inlineStr"/>
       <c r="F266" t="inlineStr">
@@ -7684,24 +7664,26 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G61</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G74</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>chr19</t>
+          <t>chr5</t>
         </is>
       </c>
       <c r="D267" t="n">
-        <v>39800000</v>
+        <v>71400000</v>
       </c>
       <c r="E267" t="inlineStr"/>
       <c r="F267" t="inlineStr">
         <is>
-          <t>SCE</t>
-        </is>
-      </c>
-      <c r="G267" t="inlineStr"/>
+          <t>Translocation</t>
+        </is>
+      </c>
+      <c r="G267" t="n">
+        <v>6.25</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -7711,16 +7693,16 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G61</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G74</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>chr22</t>
+          <t>chr5</t>
         </is>
       </c>
       <c r="D268" t="n">
-        <v>27000000</v>
+        <v>125400000</v>
       </c>
       <c r="E268" t="inlineStr"/>
       <c r="F268" t="inlineStr">
@@ -7738,16 +7720,16 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G61</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G74</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>chr3</t>
+          <t>chr6</t>
         </is>
       </c>
       <c r="D269" t="n">
-        <v>176400000</v>
+        <v>81400000</v>
       </c>
       <c r="E269" t="inlineStr"/>
       <c r="F269" t="inlineStr">
@@ -7765,16 +7747,16 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G61</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G74</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>chr5</t>
+          <t>chr6</t>
         </is>
       </c>
       <c r="D270" t="n">
-        <v>83200000</v>
+        <v>115200000</v>
       </c>
       <c r="E270" t="inlineStr"/>
       <c r="F270" t="inlineStr">
@@ -7792,16 +7774,16 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G61</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G74</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>chr7</t>
+          <t>chr6</t>
         </is>
       </c>
       <c r="D271" t="n">
-        <v>12400000</v>
+        <v>166400000</v>
       </c>
       <c r="E271" t="inlineStr"/>
       <c r="F271" t="inlineStr">
@@ -7819,16 +7801,16 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G61</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G81</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>chr8</t>
+          <t>chr1</t>
         </is>
       </c>
       <c r="D272" t="n">
-        <v>44800000</v>
+        <v>86400000</v>
       </c>
       <c r="E272" t="inlineStr"/>
       <c r="F272" t="inlineStr">
@@ -7846,16 +7828,16 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G61</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G81</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>chrX</t>
+          <t>chr1</t>
         </is>
       </c>
       <c r="D273" t="n">
-        <v>154200000</v>
+        <v>210000000</v>
       </c>
       <c r="E273" t="inlineStr"/>
       <c r="F273" t="inlineStr">
@@ -7873,16 +7855,16 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G63</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G81</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>chr1</t>
+          <t>chr10</t>
         </is>
       </c>
       <c r="D274" t="n">
-        <v>212600000</v>
+        <v>54400000</v>
       </c>
       <c r="E274" t="inlineStr"/>
       <c r="F274" t="inlineStr">
@@ -7900,16 +7882,16 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G63</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G81</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>chr10</t>
+          <t>chr14</t>
         </is>
       </c>
       <c r="D275" t="n">
-        <v>28400000</v>
+        <v>22400000</v>
       </c>
       <c r="E275" t="inlineStr"/>
       <c r="F275" t="inlineStr">
@@ -7927,26 +7909,24 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G63</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G81</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>chr10</t>
+          <t>chr14</t>
         </is>
       </c>
       <c r="D276" t="n">
-        <v>131000000</v>
+        <v>43600000</v>
       </c>
       <c r="E276" t="inlineStr"/>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Translocation</t>
-        </is>
-      </c>
-      <c r="G276" t="n">
-        <v>6.25</v>
-      </c>
+          <t>SCE</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -7956,16 +7936,16 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G63</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G81</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>chr11</t>
+          <t>chr2</t>
         </is>
       </c>
       <c r="D277" t="n">
-        <v>102600000</v>
+        <v>163200000</v>
       </c>
       <c r="E277" t="inlineStr"/>
       <c r="F277" t="inlineStr">
@@ -7983,16 +7963,16 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G63</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G81</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>chr14</t>
+          <t>chr3</t>
         </is>
       </c>
       <c r="D278" t="n">
-        <v>33400000</v>
+        <v>84800000</v>
       </c>
       <c r="E278" t="inlineStr"/>
       <c r="F278" t="inlineStr">
@@ -8010,16 +7990,16 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G63</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G81</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>chr16</t>
+          <t>chr5</t>
         </is>
       </c>
       <c r="D279" t="n">
-        <v>83800000</v>
+        <v>41600000</v>
       </c>
       <c r="E279" t="inlineStr"/>
       <c r="F279" t="inlineStr">
@@ -8037,16 +8017,16 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G63</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G81</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>chr17</t>
+          <t>chr6</t>
         </is>
       </c>
       <c r="D280" t="n">
-        <v>65600000</v>
+        <v>90200000</v>
       </c>
       <c r="E280" t="inlineStr"/>
       <c r="F280" t="inlineStr">
@@ -8064,16 +8044,16 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G64</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G81</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>chr1</t>
+          <t>chr8</t>
         </is>
       </c>
       <c r="D281" t="n">
-        <v>231800000</v>
+        <v>29000000</v>
       </c>
       <c r="E281" t="inlineStr"/>
       <c r="F281" t="inlineStr">
@@ -8091,16 +8071,16 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G64</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G81</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>chr10</t>
+          <t>chr8</t>
         </is>
       </c>
       <c r="D282" t="n">
-        <v>112800000</v>
+        <v>85800000</v>
       </c>
       <c r="E282" t="inlineStr"/>
       <c r="F282" t="inlineStr">
@@ -8118,16 +8098,16 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G64</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G81</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>chr11</t>
+          <t>chrX</t>
         </is>
       </c>
       <c r="D283" t="n">
-        <v>55600000</v>
+        <v>117200000</v>
       </c>
       <c r="E283" t="inlineStr"/>
       <c r="F283" t="inlineStr">
@@ -8145,16 +8125,16 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G64</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G86</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>chr12</t>
+          <t>chr10</t>
         </is>
       </c>
       <c r="D284" t="n">
-        <v>111000000</v>
+        <v>60000000</v>
       </c>
       <c r="E284" t="inlineStr"/>
       <c r="F284" t="inlineStr">
@@ -8172,16 +8152,16 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G64</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G86</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>chr16</t>
+          <t>chr13</t>
         </is>
       </c>
       <c r="D285" t="n">
-        <v>24000000</v>
+        <v>55200000</v>
       </c>
       <c r="E285" t="inlineStr"/>
       <c r="F285" t="inlineStr">
@@ -8199,16 +8179,16 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G64</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G86</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>chr2</t>
+          <t>chr15</t>
         </is>
       </c>
       <c r="D286" t="n">
-        <v>138200000</v>
+        <v>60200000</v>
       </c>
       <c r="E286" t="inlineStr"/>
       <c r="F286" t="inlineStr">
@@ -8226,16 +8206,16 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G64</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G86</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>chr5</t>
+          <t>chr19</t>
         </is>
       </c>
       <c r="D287" t="n">
-        <v>98200000</v>
+        <v>38800000</v>
       </c>
       <c r="E287" t="inlineStr"/>
       <c r="F287" t="inlineStr">
@@ -8253,16 +8233,16 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G64</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G86</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>chr6</t>
+          <t>chr2</t>
         </is>
       </c>
       <c r="D288" t="n">
-        <v>64000000</v>
+        <v>214800000</v>
       </c>
       <c r="E288" t="inlineStr"/>
       <c r="F288" t="inlineStr">
@@ -8280,16 +8260,16 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G64</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G86</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>chrX</t>
+          <t>chr21</t>
         </is>
       </c>
       <c r="D289" t="n">
-        <v>37400000</v>
+        <v>24200000</v>
       </c>
       <c r="E289" t="inlineStr"/>
       <c r="F289" t="inlineStr">
@@ -8307,16 +8287,16 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G74</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G86</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>chr1</t>
+          <t>chr22</t>
         </is>
       </c>
       <c r="D290" t="n">
-        <v>242400000</v>
+        <v>32200000</v>
       </c>
       <c r="E290" t="inlineStr"/>
       <c r="F290" t="inlineStr">
@@ -8334,16 +8314,16 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G74</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G86</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>chr10</t>
+          <t>chr4</t>
         </is>
       </c>
       <c r="D291" t="n">
-        <v>97600000</v>
+        <v>12800000</v>
       </c>
       <c r="E291" t="inlineStr"/>
       <c r="F291" t="inlineStr">
@@ -8361,16 +8341,16 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G74</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G86</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>chr12</t>
+          <t>chr4</t>
         </is>
       </c>
       <c r="D292" t="n">
-        <v>120600000</v>
+        <v>15600000</v>
       </c>
       <c r="E292" t="inlineStr"/>
       <c r="F292" t="inlineStr">
@@ -8388,26 +8368,24 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G74</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G86</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>chr13</t>
+          <t>chr9</t>
         </is>
       </c>
       <c r="D293" t="n">
-        <v>18400000</v>
+        <v>33200000</v>
       </c>
       <c r="E293" t="inlineStr"/>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Translocation</t>
-        </is>
-      </c>
-      <c r="G293" t="n">
-        <v>9.380000000000001</v>
-      </c>
+          <t>SCE</t>
+        </is>
+      </c>
+      <c r="G293" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -8417,16 +8395,16 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G74</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G91</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>chr13</t>
+          <t>chr11</t>
         </is>
       </c>
       <c r="D294" t="n">
-        <v>82600000</v>
+        <v>109600000</v>
       </c>
       <c r="E294" t="inlineStr"/>
       <c r="F294" t="inlineStr">
@@ -8444,7 +8422,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G74</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G91</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -8453,15 +8431,17 @@
         </is>
       </c>
       <c r="D295" t="n">
-        <v>104800000</v>
+        <v>18400000</v>
       </c>
       <c r="E295" t="inlineStr"/>
       <c r="F295" t="inlineStr">
         <is>
-          <t>SCE</t>
-        </is>
-      </c>
-      <c r="G295" t="inlineStr"/>
+          <t>Translocation</t>
+        </is>
+      </c>
+      <c r="G295" t="n">
+        <v>9.380000000000001</v>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -8471,16 +8451,16 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G74</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G91</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>chr2</t>
+          <t>chr14</t>
         </is>
       </c>
       <c r="D296" t="n">
-        <v>82000000</v>
+        <v>94200000</v>
       </c>
       <c r="E296" t="inlineStr"/>
       <c r="F296" t="inlineStr">
@@ -8498,16 +8478,16 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G74</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G91</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>chr22</t>
+          <t>chr2</t>
         </is>
       </c>
       <c r="D297" t="n">
-        <v>33600000</v>
+        <v>9400000</v>
       </c>
       <c r="E297" t="inlineStr"/>
       <c r="F297" t="inlineStr">
@@ -8525,26 +8505,24 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G74</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G91</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>chr5</t>
+          <t>chr21</t>
         </is>
       </c>
       <c r="D298" t="n">
-        <v>71400000</v>
+        <v>27000000</v>
       </c>
       <c r="E298" t="inlineStr"/>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Translocation</t>
-        </is>
-      </c>
-      <c r="G298" t="n">
-        <v>6.25</v>
-      </c>
+          <t>SCE</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -8554,16 +8532,16 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G74</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G91</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>chr5</t>
+          <t>chr3</t>
         </is>
       </c>
       <c r="D299" t="n">
-        <v>125400000</v>
+        <v>118000000</v>
       </c>
       <c r="E299" t="inlineStr"/>
       <c r="F299" t="inlineStr">
@@ -8581,16 +8559,16 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G74</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G91</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>chr6</t>
+          <t>chr5</t>
         </is>
       </c>
       <c r="D300" t="n">
-        <v>81400000</v>
+        <v>8600000</v>
       </c>
       <c r="E300" t="inlineStr"/>
       <c r="F300" t="inlineStr">
@@ -8608,16 +8586,16 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G74</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G91</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>chr6</t>
+          <t>chrX</t>
         </is>
       </c>
       <c r="D301" t="n">
-        <v>115200000</v>
+        <v>129000000</v>
       </c>
       <c r="E301" t="inlineStr"/>
       <c r="F301" t="inlineStr">
@@ -8635,16 +8613,16 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G74</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G92</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>chr6</t>
+          <t>chr12</t>
         </is>
       </c>
       <c r="D302" t="n">
-        <v>166400000</v>
+        <v>38400000</v>
       </c>
       <c r="E302" t="inlineStr"/>
       <c r="F302" t="inlineStr">
@@ -8662,16 +8640,16 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G81</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G92</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>chr1</t>
+          <t>chr12</t>
         </is>
       </c>
       <c r="D303" t="n">
-        <v>17800000</v>
+        <v>97400000</v>
       </c>
       <c r="E303" t="inlineStr"/>
       <c r="F303" t="inlineStr">
@@ -8689,16 +8667,16 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G81</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G92</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>chr1</t>
+          <t>chr13</t>
         </is>
       </c>
       <c r="D304" t="n">
-        <v>86400000</v>
+        <v>72400000</v>
       </c>
       <c r="E304" t="inlineStr"/>
       <c r="F304" t="inlineStr">
@@ -8716,16 +8694,16 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G81</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G92</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>chr1</t>
+          <t>chr13</t>
         </is>
       </c>
       <c r="D305" t="n">
-        <v>210000000</v>
+        <v>81800000</v>
       </c>
       <c r="E305" t="inlineStr"/>
       <c r="F305" t="inlineStr">
@@ -8743,16 +8721,16 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G81</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G92</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>chr10</t>
+          <t>chr13</t>
         </is>
       </c>
       <c r="D306" t="n">
-        <v>54400000</v>
+        <v>93800000</v>
       </c>
       <c r="E306" t="inlineStr"/>
       <c r="F306" t="inlineStr">
@@ -8770,7 +8748,7 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G81</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G92</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -8779,7 +8757,7 @@
         </is>
       </c>
       <c r="D307" t="n">
-        <v>22400000</v>
+        <v>79600000</v>
       </c>
       <c r="E307" t="inlineStr"/>
       <c r="F307" t="inlineStr">
@@ -8797,16 +8775,16 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G81</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G92</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>chr14</t>
+          <t>chr16</t>
         </is>
       </c>
       <c r="D308" t="n">
-        <v>43600000</v>
+        <v>59400000</v>
       </c>
       <c r="E308" t="inlineStr"/>
       <c r="F308" t="inlineStr">
@@ -8824,16 +8802,16 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G81</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G92</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>chr2</t>
+          <t>chr16</t>
         </is>
       </c>
       <c r="D309" t="n">
-        <v>163200000</v>
+        <v>66000000</v>
       </c>
       <c r="E309" t="inlineStr"/>
       <c r="F309" t="inlineStr">
@@ -8851,16 +8829,16 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G81</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G92</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>chr3</t>
+          <t>chr2</t>
         </is>
       </c>
       <c r="D310" t="n">
-        <v>84800000</v>
+        <v>106000000</v>
       </c>
       <c r="E310" t="inlineStr"/>
       <c r="F310" t="inlineStr">
@@ -8878,16 +8856,16 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G81</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G92</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>chr5</t>
+          <t>chr2</t>
         </is>
       </c>
       <c r="D311" t="n">
-        <v>41600000</v>
+        <v>190600000</v>
       </c>
       <c r="E311" t="inlineStr"/>
       <c r="F311" t="inlineStr">
@@ -8905,16 +8883,16 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G81</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G92</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>chr6</t>
+          <t>chr20</t>
         </is>
       </c>
       <c r="D312" t="n">
-        <v>90200000</v>
+        <v>14000000</v>
       </c>
       <c r="E312" t="inlineStr"/>
       <c r="F312" t="inlineStr">
@@ -8932,16 +8910,16 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G81</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G92</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>chr8</t>
+          <t>chr6</t>
         </is>
       </c>
       <c r="D313" t="n">
-        <v>29000000</v>
+        <v>21600000</v>
       </c>
       <c r="E313" t="inlineStr"/>
       <c r="F313" t="inlineStr">
@@ -8959,16 +8937,16 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G81</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G92</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>chr8</t>
+          <t>chrX</t>
         </is>
       </c>
       <c r="D314" t="n">
-        <v>85800000</v>
+        <v>58600000</v>
       </c>
       <c r="E314" t="inlineStr"/>
       <c r="F314" t="inlineStr">
@@ -8977,957 +8955,6 @@
         </is>
       </c>
       <c r="G314" t="inlineStr"/>
-    </row>
-    <row r="315">
-      <c r="A315" t="inlineStr">
-        <is>
-          <t>fastq0022_HPNE_M</t>
-        </is>
-      </c>
-      <c r="B315" t="inlineStr">
-        <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G81</t>
-        </is>
-      </c>
-      <c r="C315" t="inlineStr">
-        <is>
-          <t>chrX</t>
-        </is>
-      </c>
-      <c r="D315" t="n">
-        <v>117200000</v>
-      </c>
-      <c r="E315" t="inlineStr"/>
-      <c r="F315" t="inlineStr">
-        <is>
-          <t>SCE</t>
-        </is>
-      </c>
-      <c r="G315" t="inlineStr"/>
-    </row>
-    <row r="316">
-      <c r="A316" t="inlineStr">
-        <is>
-          <t>fastq0022_HPNE_M</t>
-        </is>
-      </c>
-      <c r="B316" t="inlineStr">
-        <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G86</t>
-        </is>
-      </c>
-      <c r="C316" t="inlineStr">
-        <is>
-          <t>chr10</t>
-        </is>
-      </c>
-      <c r="D316" t="n">
-        <v>60000000</v>
-      </c>
-      <c r="E316" t="inlineStr"/>
-      <c r="F316" t="inlineStr">
-        <is>
-          <t>SCE</t>
-        </is>
-      </c>
-      <c r="G316" t="inlineStr"/>
-    </row>
-    <row r="317">
-      <c r="A317" t="inlineStr">
-        <is>
-          <t>fastq0022_HPNE_M</t>
-        </is>
-      </c>
-      <c r="B317" t="inlineStr">
-        <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G86</t>
-        </is>
-      </c>
-      <c r="C317" t="inlineStr">
-        <is>
-          <t>chr13</t>
-        </is>
-      </c>
-      <c r="D317" t="n">
-        <v>55200000</v>
-      </c>
-      <c r="E317" t="inlineStr"/>
-      <c r="F317" t="inlineStr">
-        <is>
-          <t>SCE</t>
-        </is>
-      </c>
-      <c r="G317" t="inlineStr"/>
-    </row>
-    <row r="318">
-      <c r="A318" t="inlineStr">
-        <is>
-          <t>fastq0022_HPNE_M</t>
-        </is>
-      </c>
-      <c r="B318" t="inlineStr">
-        <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G86</t>
-        </is>
-      </c>
-      <c r="C318" t="inlineStr">
-        <is>
-          <t>chr15</t>
-        </is>
-      </c>
-      <c r="D318" t="n">
-        <v>60200000</v>
-      </c>
-      <c r="E318" t="inlineStr"/>
-      <c r="F318" t="inlineStr">
-        <is>
-          <t>SCE</t>
-        </is>
-      </c>
-      <c r="G318" t="inlineStr"/>
-    </row>
-    <row r="319">
-      <c r="A319" t="inlineStr">
-        <is>
-          <t>fastq0022_HPNE_M</t>
-        </is>
-      </c>
-      <c r="B319" t="inlineStr">
-        <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G86</t>
-        </is>
-      </c>
-      <c r="C319" t="inlineStr">
-        <is>
-          <t>chr19</t>
-        </is>
-      </c>
-      <c r="D319" t="n">
-        <v>38800000</v>
-      </c>
-      <c r="E319" t="inlineStr"/>
-      <c r="F319" t="inlineStr">
-        <is>
-          <t>SCE</t>
-        </is>
-      </c>
-      <c r="G319" t="inlineStr"/>
-    </row>
-    <row r="320">
-      <c r="A320" t="inlineStr">
-        <is>
-          <t>fastq0022_HPNE_M</t>
-        </is>
-      </c>
-      <c r="B320" t="inlineStr">
-        <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G86</t>
-        </is>
-      </c>
-      <c r="C320" t="inlineStr">
-        <is>
-          <t>chr2</t>
-        </is>
-      </c>
-      <c r="D320" t="n">
-        <v>214800000</v>
-      </c>
-      <c r="E320" t="inlineStr"/>
-      <c r="F320" t="inlineStr">
-        <is>
-          <t>SCE</t>
-        </is>
-      </c>
-      <c r="G320" t="inlineStr"/>
-    </row>
-    <row r="321">
-      <c r="A321" t="inlineStr">
-        <is>
-          <t>fastq0022_HPNE_M</t>
-        </is>
-      </c>
-      <c r="B321" t="inlineStr">
-        <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G86</t>
-        </is>
-      </c>
-      <c r="C321" t="inlineStr">
-        <is>
-          <t>chr21</t>
-        </is>
-      </c>
-      <c r="D321" t="n">
-        <v>24200000</v>
-      </c>
-      <c r="E321" t="inlineStr"/>
-      <c r="F321" t="inlineStr">
-        <is>
-          <t>SCE</t>
-        </is>
-      </c>
-      <c r="G321" t="inlineStr"/>
-    </row>
-    <row r="322">
-      <c r="A322" t="inlineStr">
-        <is>
-          <t>fastq0022_HPNE_M</t>
-        </is>
-      </c>
-      <c r="B322" t="inlineStr">
-        <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G86</t>
-        </is>
-      </c>
-      <c r="C322" t="inlineStr">
-        <is>
-          <t>chr22</t>
-        </is>
-      </c>
-      <c r="D322" t="n">
-        <v>32200000</v>
-      </c>
-      <c r="E322" t="inlineStr"/>
-      <c r="F322" t="inlineStr">
-        <is>
-          <t>SCE</t>
-        </is>
-      </c>
-      <c r="G322" t="inlineStr"/>
-    </row>
-    <row r="323">
-      <c r="A323" t="inlineStr">
-        <is>
-          <t>fastq0022_HPNE_M</t>
-        </is>
-      </c>
-      <c r="B323" t="inlineStr">
-        <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G86</t>
-        </is>
-      </c>
-      <c r="C323" t="inlineStr">
-        <is>
-          <t>chr4</t>
-        </is>
-      </c>
-      <c r="D323" t="n">
-        <v>12800000</v>
-      </c>
-      <c r="E323" t="inlineStr"/>
-      <c r="F323" t="inlineStr">
-        <is>
-          <t>SCE</t>
-        </is>
-      </c>
-      <c r="G323" t="inlineStr"/>
-    </row>
-    <row r="324">
-      <c r="A324" t="inlineStr">
-        <is>
-          <t>fastq0022_HPNE_M</t>
-        </is>
-      </c>
-      <c r="B324" t="inlineStr">
-        <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G86</t>
-        </is>
-      </c>
-      <c r="C324" t="inlineStr">
-        <is>
-          <t>chr4</t>
-        </is>
-      </c>
-      <c r="D324" t="n">
-        <v>15600000</v>
-      </c>
-      <c r="E324" t="inlineStr"/>
-      <c r="F324" t="inlineStr">
-        <is>
-          <t>SCE</t>
-        </is>
-      </c>
-      <c r="G324" t="inlineStr"/>
-    </row>
-    <row r="325">
-      <c r="A325" t="inlineStr">
-        <is>
-          <t>fastq0022_HPNE_M</t>
-        </is>
-      </c>
-      <c r="B325" t="inlineStr">
-        <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G86</t>
-        </is>
-      </c>
-      <c r="C325" t="inlineStr">
-        <is>
-          <t>chr9</t>
-        </is>
-      </c>
-      <c r="D325" t="n">
-        <v>33200000</v>
-      </c>
-      <c r="E325" t="inlineStr"/>
-      <c r="F325" t="inlineStr">
-        <is>
-          <t>SCE</t>
-        </is>
-      </c>
-      <c r="G325" t="inlineStr"/>
-    </row>
-    <row r="326">
-      <c r="A326" t="inlineStr">
-        <is>
-          <t>fastq0022_HPNE_M</t>
-        </is>
-      </c>
-      <c r="B326" t="inlineStr">
-        <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G91</t>
-        </is>
-      </c>
-      <c r="C326" t="inlineStr">
-        <is>
-          <t>chr11</t>
-        </is>
-      </c>
-      <c r="D326" t="n">
-        <v>109600000</v>
-      </c>
-      <c r="E326" t="inlineStr"/>
-      <c r="F326" t="inlineStr">
-        <is>
-          <t>SCE</t>
-        </is>
-      </c>
-      <c r="G326" t="inlineStr"/>
-    </row>
-    <row r="327">
-      <c r="A327" t="inlineStr">
-        <is>
-          <t>fastq0022_HPNE_M</t>
-        </is>
-      </c>
-      <c r="B327" t="inlineStr">
-        <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G91</t>
-        </is>
-      </c>
-      <c r="C327" t="inlineStr">
-        <is>
-          <t>chr13</t>
-        </is>
-      </c>
-      <c r="D327" t="n">
-        <v>18400000</v>
-      </c>
-      <c r="E327" t="inlineStr"/>
-      <c r="F327" t="inlineStr">
-        <is>
-          <t>Translocation</t>
-        </is>
-      </c>
-      <c r="G327" t="n">
-        <v>9.380000000000001</v>
-      </c>
-    </row>
-    <row r="328">
-      <c r="A328" t="inlineStr">
-        <is>
-          <t>fastq0022_HPNE_M</t>
-        </is>
-      </c>
-      <c r="B328" t="inlineStr">
-        <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G91</t>
-        </is>
-      </c>
-      <c r="C328" t="inlineStr">
-        <is>
-          <t>chr14</t>
-        </is>
-      </c>
-      <c r="D328" t="n">
-        <v>94200000</v>
-      </c>
-      <c r="E328" t="inlineStr"/>
-      <c r="F328" t="inlineStr">
-        <is>
-          <t>SCE</t>
-        </is>
-      </c>
-      <c r="G328" t="inlineStr"/>
-    </row>
-    <row r="329">
-      <c r="A329" t="inlineStr">
-        <is>
-          <t>fastq0022_HPNE_M</t>
-        </is>
-      </c>
-      <c r="B329" t="inlineStr">
-        <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G91</t>
-        </is>
-      </c>
-      <c r="C329" t="inlineStr">
-        <is>
-          <t>chr2</t>
-        </is>
-      </c>
-      <c r="D329" t="n">
-        <v>9400000</v>
-      </c>
-      <c r="E329" t="inlineStr"/>
-      <c r="F329" t="inlineStr">
-        <is>
-          <t>SCE</t>
-        </is>
-      </c>
-      <c r="G329" t="inlineStr"/>
-    </row>
-    <row r="330">
-      <c r="A330" t="inlineStr">
-        <is>
-          <t>fastq0022_HPNE_M</t>
-        </is>
-      </c>
-      <c r="B330" t="inlineStr">
-        <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G91</t>
-        </is>
-      </c>
-      <c r="C330" t="inlineStr">
-        <is>
-          <t>chr21</t>
-        </is>
-      </c>
-      <c r="D330" t="n">
-        <v>27000000</v>
-      </c>
-      <c r="E330" t="inlineStr"/>
-      <c r="F330" t="inlineStr">
-        <is>
-          <t>SCE</t>
-        </is>
-      </c>
-      <c r="G330" t="inlineStr"/>
-    </row>
-    <row r="331">
-      <c r="A331" t="inlineStr">
-        <is>
-          <t>fastq0022_HPNE_M</t>
-        </is>
-      </c>
-      <c r="B331" t="inlineStr">
-        <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G91</t>
-        </is>
-      </c>
-      <c r="C331" t="inlineStr">
-        <is>
-          <t>chr3</t>
-        </is>
-      </c>
-      <c r="D331" t="n">
-        <v>118000000</v>
-      </c>
-      <c r="E331" t="inlineStr"/>
-      <c r="F331" t="inlineStr">
-        <is>
-          <t>SCE</t>
-        </is>
-      </c>
-      <c r="G331" t="inlineStr"/>
-    </row>
-    <row r="332">
-      <c r="A332" t="inlineStr">
-        <is>
-          <t>fastq0022_HPNE_M</t>
-        </is>
-      </c>
-      <c r="B332" t="inlineStr">
-        <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G91</t>
-        </is>
-      </c>
-      <c r="C332" t="inlineStr">
-        <is>
-          <t>chrX</t>
-        </is>
-      </c>
-      <c r="D332" t="n">
-        <v>129000000</v>
-      </c>
-      <c r="E332" t="inlineStr"/>
-      <c r="F332" t="inlineStr">
-        <is>
-          <t>SCE</t>
-        </is>
-      </c>
-      <c r="G332" t="inlineStr"/>
-    </row>
-    <row r="333">
-      <c r="A333" t="inlineStr">
-        <is>
-          <t>fastq0022_HPNE_M</t>
-        </is>
-      </c>
-      <c r="B333" t="inlineStr">
-        <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G92</t>
-        </is>
-      </c>
-      <c r="C333" t="inlineStr">
-        <is>
-          <t>chr12</t>
-        </is>
-      </c>
-      <c r="D333" t="n">
-        <v>38400000</v>
-      </c>
-      <c r="E333" t="inlineStr"/>
-      <c r="F333" t="inlineStr">
-        <is>
-          <t>SCE</t>
-        </is>
-      </c>
-      <c r="G333" t="inlineStr"/>
-    </row>
-    <row r="334">
-      <c r="A334" t="inlineStr">
-        <is>
-          <t>fastq0022_HPNE_M</t>
-        </is>
-      </c>
-      <c r="B334" t="inlineStr">
-        <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G92</t>
-        </is>
-      </c>
-      <c r="C334" t="inlineStr">
-        <is>
-          <t>chr12</t>
-        </is>
-      </c>
-      <c r="D334" t="n">
-        <v>97400000</v>
-      </c>
-      <c r="E334" t="inlineStr"/>
-      <c r="F334" t="inlineStr">
-        <is>
-          <t>SCE</t>
-        </is>
-      </c>
-      <c r="G334" t="inlineStr"/>
-    </row>
-    <row r="335">
-      <c r="A335" t="inlineStr">
-        <is>
-          <t>fastq0022_HPNE_M</t>
-        </is>
-      </c>
-      <c r="B335" t="inlineStr">
-        <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G92</t>
-        </is>
-      </c>
-      <c r="C335" t="inlineStr">
-        <is>
-          <t>chr13</t>
-        </is>
-      </c>
-      <c r="D335" t="n">
-        <v>72400000</v>
-      </c>
-      <c r="E335" t="inlineStr"/>
-      <c r="F335" t="inlineStr">
-        <is>
-          <t>SCE</t>
-        </is>
-      </c>
-      <c r="G335" t="inlineStr"/>
-    </row>
-    <row r="336">
-      <c r="A336" t="inlineStr">
-        <is>
-          <t>fastq0022_HPNE_M</t>
-        </is>
-      </c>
-      <c r="B336" t="inlineStr">
-        <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G92</t>
-        </is>
-      </c>
-      <c r="C336" t="inlineStr">
-        <is>
-          <t>chr13</t>
-        </is>
-      </c>
-      <c r="D336" t="n">
-        <v>81800000</v>
-      </c>
-      <c r="E336" t="inlineStr"/>
-      <c r="F336" t="inlineStr">
-        <is>
-          <t>SCE</t>
-        </is>
-      </c>
-      <c r="G336" t="inlineStr"/>
-    </row>
-    <row r="337">
-      <c r="A337" t="inlineStr">
-        <is>
-          <t>fastq0022_HPNE_M</t>
-        </is>
-      </c>
-      <c r="B337" t="inlineStr">
-        <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G92</t>
-        </is>
-      </c>
-      <c r="C337" t="inlineStr">
-        <is>
-          <t>chr13</t>
-        </is>
-      </c>
-      <c r="D337" t="n">
-        <v>93800000</v>
-      </c>
-      <c r="E337" t="inlineStr"/>
-      <c r="F337" t="inlineStr">
-        <is>
-          <t>SCE</t>
-        </is>
-      </c>
-      <c r="G337" t="inlineStr"/>
-    </row>
-    <row r="338">
-      <c r="A338" t="inlineStr">
-        <is>
-          <t>fastq0022_HPNE_M</t>
-        </is>
-      </c>
-      <c r="B338" t="inlineStr">
-        <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G92</t>
-        </is>
-      </c>
-      <c r="C338" t="inlineStr">
-        <is>
-          <t>chr14</t>
-        </is>
-      </c>
-      <c r="D338" t="n">
-        <v>79600000</v>
-      </c>
-      <c r="E338" t="inlineStr"/>
-      <c r="F338" t="inlineStr">
-        <is>
-          <t>SCE</t>
-        </is>
-      </c>
-      <c r="G338" t="inlineStr"/>
-    </row>
-    <row r="339">
-      <c r="A339" t="inlineStr">
-        <is>
-          <t>fastq0022_HPNE_M</t>
-        </is>
-      </c>
-      <c r="B339" t="inlineStr">
-        <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G92</t>
-        </is>
-      </c>
-      <c r="C339" t="inlineStr">
-        <is>
-          <t>chr16</t>
-        </is>
-      </c>
-      <c r="D339" t="n">
-        <v>59400000</v>
-      </c>
-      <c r="E339" t="inlineStr"/>
-      <c r="F339" t="inlineStr">
-        <is>
-          <t>SCE</t>
-        </is>
-      </c>
-      <c r="G339" t="inlineStr"/>
-    </row>
-    <row r="340">
-      <c r="A340" t="inlineStr">
-        <is>
-          <t>fastq0022_HPNE_M</t>
-        </is>
-      </c>
-      <c r="B340" t="inlineStr">
-        <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G92</t>
-        </is>
-      </c>
-      <c r="C340" t="inlineStr">
-        <is>
-          <t>chr16</t>
-        </is>
-      </c>
-      <c r="D340" t="n">
-        <v>66000000</v>
-      </c>
-      <c r="E340" t="inlineStr"/>
-      <c r="F340" t="inlineStr">
-        <is>
-          <t>SCE</t>
-        </is>
-      </c>
-      <c r="G340" t="inlineStr"/>
-    </row>
-    <row r="341">
-      <c r="A341" t="inlineStr">
-        <is>
-          <t>fastq0022_HPNE_M</t>
-        </is>
-      </c>
-      <c r="B341" t="inlineStr">
-        <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G92</t>
-        </is>
-      </c>
-      <c r="C341" t="inlineStr">
-        <is>
-          <t>chr2</t>
-        </is>
-      </c>
-      <c r="D341" t="n">
-        <v>77000000</v>
-      </c>
-      <c r="E341" t="inlineStr"/>
-      <c r="F341" t="inlineStr">
-        <is>
-          <t>SCE</t>
-        </is>
-      </c>
-      <c r="G341" t="inlineStr"/>
-    </row>
-    <row r="342">
-      <c r="A342" t="inlineStr">
-        <is>
-          <t>fastq0022_HPNE_M</t>
-        </is>
-      </c>
-      <c r="B342" t="inlineStr">
-        <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G92</t>
-        </is>
-      </c>
-      <c r="C342" t="inlineStr">
-        <is>
-          <t>chr2</t>
-        </is>
-      </c>
-      <c r="D342" t="n">
-        <v>82400000</v>
-      </c>
-      <c r="E342" t="inlineStr"/>
-      <c r="F342" t="inlineStr">
-        <is>
-          <t>Translocation</t>
-        </is>
-      </c>
-      <c r="G342" t="n">
-        <v>6.25</v>
-      </c>
-    </row>
-    <row r="343">
-      <c r="A343" t="inlineStr">
-        <is>
-          <t>fastq0022_HPNE_M</t>
-        </is>
-      </c>
-      <c r="B343" t="inlineStr">
-        <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G92</t>
-        </is>
-      </c>
-      <c r="C343" t="inlineStr">
-        <is>
-          <t>chr2</t>
-        </is>
-      </c>
-      <c r="D343" t="n">
-        <v>106000000</v>
-      </c>
-      <c r="E343" t="inlineStr"/>
-      <c r="F343" t="inlineStr">
-        <is>
-          <t>SCE</t>
-        </is>
-      </c>
-      <c r="G343" t="inlineStr"/>
-    </row>
-    <row r="344">
-      <c r="A344" t="inlineStr">
-        <is>
-          <t>fastq0022_HPNE_M</t>
-        </is>
-      </c>
-      <c r="B344" t="inlineStr">
-        <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G92</t>
-        </is>
-      </c>
-      <c r="C344" t="inlineStr">
-        <is>
-          <t>chr2</t>
-        </is>
-      </c>
-      <c r="D344" t="n">
-        <v>190600000</v>
-      </c>
-      <c r="E344" t="inlineStr"/>
-      <c r="F344" t="inlineStr">
-        <is>
-          <t>SCE</t>
-        </is>
-      </c>
-      <c r="G344" t="inlineStr"/>
-    </row>
-    <row r="345">
-      <c r="A345" t="inlineStr">
-        <is>
-          <t>fastq0022_HPNE_M</t>
-        </is>
-      </c>
-      <c r="B345" t="inlineStr">
-        <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G92</t>
-        </is>
-      </c>
-      <c r="C345" t="inlineStr">
-        <is>
-          <t>chr20</t>
-        </is>
-      </c>
-      <c r="D345" t="n">
-        <v>14000000</v>
-      </c>
-      <c r="E345" t="inlineStr"/>
-      <c r="F345" t="inlineStr">
-        <is>
-          <t>SCE</t>
-        </is>
-      </c>
-      <c r="G345" t="inlineStr"/>
-    </row>
-    <row r="346">
-      <c r="A346" t="inlineStr">
-        <is>
-          <t>fastq0022_HPNE_M</t>
-        </is>
-      </c>
-      <c r="B346" t="inlineStr">
-        <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G92</t>
-        </is>
-      </c>
-      <c r="C346" t="inlineStr">
-        <is>
-          <t>chr5</t>
-        </is>
-      </c>
-      <c r="D346" t="n">
-        <v>18400000</v>
-      </c>
-      <c r="E346" t="inlineStr"/>
-      <c r="F346" t="inlineStr">
-        <is>
-          <t>SCE</t>
-        </is>
-      </c>
-      <c r="G346" t="inlineStr"/>
-    </row>
-    <row r="347">
-      <c r="A347" t="inlineStr">
-        <is>
-          <t>fastq0022_HPNE_M</t>
-        </is>
-      </c>
-      <c r="B347" t="inlineStr">
-        <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G92</t>
-        </is>
-      </c>
-      <c r="C347" t="inlineStr">
-        <is>
-          <t>chr5</t>
-        </is>
-      </c>
-      <c r="D347" t="n">
-        <v>26600000</v>
-      </c>
-      <c r="E347" t="inlineStr"/>
-      <c r="F347" t="inlineStr">
-        <is>
-          <t>Translocation</t>
-        </is>
-      </c>
-      <c r="G347" t="n">
-        <v>6.25</v>
-      </c>
-    </row>
-    <row r="348">
-      <c r="A348" t="inlineStr">
-        <is>
-          <t>fastq0022_HPNE_M</t>
-        </is>
-      </c>
-      <c r="B348" t="inlineStr">
-        <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G92</t>
-        </is>
-      </c>
-      <c r="C348" t="inlineStr">
-        <is>
-          <t>chr6</t>
-        </is>
-      </c>
-      <c r="D348" t="n">
-        <v>21600000</v>
-      </c>
-      <c r="E348" t="inlineStr"/>
-      <c r="F348" t="inlineStr">
-        <is>
-          <t>SCE</t>
-        </is>
-      </c>
-      <c r="G348" t="inlineStr"/>
-    </row>
-    <row r="349">
-      <c r="A349" t="inlineStr">
-        <is>
-          <t>fastq0022_HPNE_M</t>
-        </is>
-      </c>
-      <c r="B349" t="inlineStr">
-        <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G92</t>
-        </is>
-      </c>
-      <c r="C349" t="inlineStr">
-        <is>
-          <t>chrX</t>
-        </is>
-      </c>
-      <c r="D349" t="n">
-        <v>58600000</v>
-      </c>
-      <c r="E349" t="inlineStr"/>
-      <c r="F349" t="inlineStr">
-        <is>
-          <t>SCE</t>
-        </is>
-      </c>
-      <c r="G349" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/SCE_detected.xlsx
+++ b/SCE_detected.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G314"/>
+  <dimension ref="A1:G316"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3134,11 +3134,11 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>chr4</t>
+          <t>chr22</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>156000000</v>
+        <v>33800000</v>
       </c>
       <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr">
@@ -3161,11 +3161,11 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>chr9</t>
+          <t>chr4</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>80200000</v>
+        <v>156000000</v>
       </c>
       <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr">
@@ -3183,16 +3183,16 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G24</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G20</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>chr1</t>
+          <t>chr9</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>9400000</v>
+        <v>80200000</v>
       </c>
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr">
@@ -3215,11 +3215,11 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>chr18</t>
+          <t>chr1</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>30800000</v>
+        <v>9400000</v>
       </c>
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr">
@@ -3242,11 +3242,11 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>chr5</t>
+          <t>chr18</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>60400000</v>
+        <v>30800000</v>
       </c>
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr">
@@ -3269,11 +3269,11 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>chr9</t>
+          <t>chr5</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>83800000</v>
+        <v>60400000</v>
       </c>
       <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr">
@@ -3291,16 +3291,16 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G25</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G24</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>chr1</t>
+          <t>chr9</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>35600000</v>
+        <v>83800000</v>
       </c>
       <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr">
@@ -3323,11 +3323,11 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>chr10</t>
+          <t>chr1</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>75600000</v>
+        <v>35600000</v>
       </c>
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr">
@@ -3350,11 +3350,11 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>chr11</t>
+          <t>chr10</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>18400000</v>
+        <v>75600000</v>
       </c>
       <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr">
@@ -3377,11 +3377,11 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>chr12</t>
+          <t>chr11</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>1800000</v>
+        <v>18400000</v>
       </c>
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr">
@@ -3408,7 +3408,7 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>12800000</v>
+        <v>1800000</v>
       </c>
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr">
@@ -3435,7 +3435,7 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>43600000</v>
+        <v>12800000</v>
       </c>
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr">
@@ -3458,11 +3458,11 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>chr2</t>
+          <t>chr12</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>182400000</v>
+        <v>43600000</v>
       </c>
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr">
@@ -3485,11 +3485,11 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>chr5</t>
+          <t>chr2</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>119800000</v>
+        <v>182400000</v>
       </c>
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr">
@@ -3512,11 +3512,11 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>chrX</t>
+          <t>chr5</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>81000000</v>
+        <v>119800000</v>
       </c>
       <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr">
@@ -3534,16 +3534,16 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G26</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G25</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>chr11</t>
+          <t>chrX</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>46000000</v>
+        <v>81000000</v>
       </c>
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr">
@@ -3570,7 +3570,7 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>85600000</v>
+        <v>46000000</v>
       </c>
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr">
@@ -3593,11 +3593,11 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>chr12</t>
+          <t>chr11</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>72600000</v>
+        <v>85600000</v>
       </c>
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr">
@@ -3620,11 +3620,11 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>chr14</t>
+          <t>chr12</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>76600000</v>
+        <v>72600000</v>
       </c>
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr">
@@ -3647,11 +3647,11 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>chr16</t>
+          <t>chr14</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>30200000</v>
+        <v>76600000</v>
       </c>
       <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr">
@@ -3674,11 +3674,11 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>chr18</t>
+          <t>chr16</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>45600000</v>
+        <v>30200000</v>
       </c>
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr">
@@ -3701,11 +3701,11 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>chr19</t>
+          <t>chr18</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>52400000</v>
+        <v>45600000</v>
       </c>
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr">
@@ -3728,11 +3728,11 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>chr2</t>
+          <t>chr19</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>69400000</v>
+        <v>52400000</v>
       </c>
       <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr">
@@ -3755,11 +3755,11 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>chr5</t>
+          <t>chr2</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>142600000</v>
+        <v>69400000</v>
       </c>
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr">
@@ -3782,11 +3782,11 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>chr6</t>
+          <t>chr5</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>55400000</v>
+        <v>142600000</v>
       </c>
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr">
@@ -3809,21 +3809,19 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>chr8</t>
+          <t>chr6</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>65400000</v>
+        <v>55400000</v>
       </c>
       <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Translocation</t>
-        </is>
-      </c>
-      <c r="G125" t="n">
-        <v>6.25</v>
-      </c>
+          <t>SCE</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -3833,24 +3831,26 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G27</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G26</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>chr1</t>
+          <t>chr8</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>30200000</v>
+        <v>65400000</v>
       </c>
       <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr">
         <is>
-          <t>SCE</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr"/>
+          <t>Translocation</t>
+        </is>
+      </c>
+      <c r="G126" t="n">
+        <v>6.25</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -3869,7 +3869,7 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>182400000</v>
+        <v>30200000</v>
       </c>
       <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr">
@@ -3892,11 +3892,11 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>chr10</t>
+          <t>chr1</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>43200000</v>
+        <v>182400000</v>
       </c>
       <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr">
@@ -3919,11 +3919,11 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>chr11</t>
+          <t>chr10</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>127200000</v>
+        <v>43200000</v>
       </c>
       <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr">
@@ -3946,11 +3946,11 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>chr13</t>
+          <t>chr11</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>75800000</v>
+        <v>127200000</v>
       </c>
       <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr">
@@ -3973,11 +3973,11 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>chr16</t>
+          <t>chr13</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>53000000</v>
+        <v>75800000</v>
       </c>
       <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr">
@@ -4000,11 +4000,11 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>chr18</t>
+          <t>chr16</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>24400000</v>
+        <v>53000000</v>
       </c>
       <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr">
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>58400000</v>
+        <v>24400000</v>
       </c>
       <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr">
@@ -4054,11 +4054,11 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>chr2</t>
+          <t>chr18</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>29400000</v>
+        <v>58400000</v>
       </c>
       <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr">
@@ -4081,11 +4081,11 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>chr3</t>
+          <t>chr2</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>66800000</v>
+        <v>29400000</v>
       </c>
       <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr">
@@ -4103,16 +4103,16 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G28</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G27</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>chr1</t>
+          <t>chr3</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>30800000</v>
+        <v>66800000</v>
       </c>
       <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr">
@@ -4135,11 +4135,11 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>chr10</t>
+          <t>chr1</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>16800000</v>
+        <v>30800000</v>
       </c>
       <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr">
@@ -4162,11 +4162,11 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>chr11</t>
+          <t>chr10</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>63000000</v>
+        <v>16800000</v>
       </c>
       <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr">
@@ -4189,11 +4189,11 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>chr12</t>
+          <t>chr11</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>99600000</v>
+        <v>63000000</v>
       </c>
       <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr">
@@ -4216,11 +4216,11 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>chr21</t>
+          <t>chr12</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>25800000</v>
+        <v>99600000</v>
       </c>
       <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr">
@@ -4243,11 +4243,11 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>chr22</t>
+          <t>chr21</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>42200000</v>
+        <v>25800000</v>
       </c>
       <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr">
@@ -4270,11 +4270,11 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>chr4</t>
+          <t>chr22</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>41000000</v>
+        <v>42200000</v>
       </c>
       <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr">
@@ -4297,11 +4297,11 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>chr7</t>
+          <t>chr4</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>5600000</v>
+        <v>41000000</v>
       </c>
       <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr">
@@ -4328,7 +4328,7 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>19800000</v>
+        <v>5600000</v>
       </c>
       <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr">
@@ -4346,16 +4346,16 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G30</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G28</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>chr1</t>
+          <t>chr7</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>219400000</v>
+        <v>19800000</v>
       </c>
       <c r="E145" t="inlineStr"/>
       <c r="F145" t="inlineStr">
@@ -4378,11 +4378,11 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>chr12</t>
+          <t>chr1</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>78000000</v>
+        <v>219400000</v>
       </c>
       <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr">
@@ -4405,11 +4405,11 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>chr14</t>
+          <t>chr12</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>43200000</v>
+        <v>78000000</v>
       </c>
       <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr">
@@ -4436,7 +4436,7 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>66800000</v>
+        <v>43200000</v>
       </c>
       <c r="E148" t="inlineStr"/>
       <c r="F148" t="inlineStr">
@@ -4459,11 +4459,11 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>chr2</t>
+          <t>chr14</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>52000000</v>
+        <v>66800000</v>
       </c>
       <c r="E149" t="inlineStr"/>
       <c r="F149" t="inlineStr">
@@ -4486,11 +4486,11 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>chr3</t>
+          <t>chr2</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>151400000</v>
+        <v>52000000</v>
       </c>
       <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr">
@@ -4513,11 +4513,11 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>chr4</t>
+          <t>chr3</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>182800000</v>
+        <v>151400000</v>
       </c>
       <c r="E151" t="inlineStr"/>
       <c r="F151" t="inlineStr">
@@ -4540,11 +4540,11 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>chr6</t>
+          <t>chr4</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>56600000</v>
+        <v>182800000</v>
       </c>
       <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr">
@@ -4562,16 +4562,16 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G32</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G30</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>chr11</t>
+          <t>chr6</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>13800000</v>
+        <v>56600000</v>
       </c>
       <c r="E153" t="inlineStr"/>
       <c r="F153" t="inlineStr">
@@ -4594,21 +4594,19 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>chr13</t>
+          <t>chr11</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>18400000</v>
+        <v>13800000</v>
       </c>
       <c r="E154" t="inlineStr"/>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Translocation</t>
-        </is>
-      </c>
-      <c r="G154" t="n">
-        <v>9.380000000000001</v>
-      </c>
+          <t>SCE</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -4623,19 +4621,21 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>chr15</t>
+          <t>chr13</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>40800000</v>
+        <v>18400000</v>
       </c>
       <c r="E155" t="inlineStr"/>
       <c r="F155" t="inlineStr">
         <is>
-          <t>SCE</t>
-        </is>
-      </c>
-      <c r="G155" t="inlineStr"/>
+          <t>Translocation</t>
+        </is>
+      </c>
+      <c r="G155" t="n">
+        <v>9.380000000000001</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -4650,11 +4650,11 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>chr16</t>
+          <t>chr15</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>72000000</v>
+        <v>40800000</v>
       </c>
       <c r="E156" t="inlineStr"/>
       <c r="F156" t="inlineStr">
@@ -4677,11 +4677,11 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>chr18</t>
+          <t>chr16</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>40400000</v>
+        <v>72000000</v>
       </c>
       <c r="E157" t="inlineStr"/>
       <c r="F157" t="inlineStr">
@@ -4704,21 +4704,19 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>chr20</t>
+          <t>chr18</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>31200000</v>
+        <v>40400000</v>
       </c>
       <c r="E158" t="inlineStr"/>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Translocation</t>
-        </is>
-      </c>
-      <c r="G158" t="n">
-        <v>9.380000000000001</v>
-      </c>
+          <t>SCE</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -4733,19 +4731,21 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>chr3</t>
+          <t>chr20</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>56400000</v>
+        <v>31200000</v>
       </c>
       <c r="E159" t="inlineStr"/>
       <c r="F159" t="inlineStr">
         <is>
-          <t>SCE</t>
-        </is>
-      </c>
-      <c r="G159" t="inlineStr"/>
+          <t>Translocation</t>
+        </is>
+      </c>
+      <c r="G159" t="n">
+        <v>9.380000000000001</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -4764,7 +4764,7 @@
         </is>
       </c>
       <c r="D160" t="n">
-        <v>151000000</v>
+        <v>56400000</v>
       </c>
       <c r="E160" t="inlineStr"/>
       <c r="F160" t="inlineStr">
@@ -4787,21 +4787,19 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>chr5</t>
+          <t>chr3</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>71400000</v>
+        <v>151000000</v>
       </c>
       <c r="E161" t="inlineStr"/>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Translocation</t>
-        </is>
-      </c>
-      <c r="G161" t="n">
-        <v>6.25</v>
-      </c>
+          <t>SCE</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -4816,11 +4814,11 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>chr9</t>
+          <t>chr5</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>69400000</v>
+        <v>71400000</v>
       </c>
       <c r="E162" t="inlineStr"/>
       <c r="F162" t="inlineStr">
@@ -4840,24 +4838,26 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G37</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G32</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>chr12</t>
+          <t>chr9</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>95600000</v>
+        <v>69400000</v>
       </c>
       <c r="E163" t="inlineStr"/>
       <c r="F163" t="inlineStr">
         <is>
-          <t>SCE</t>
-        </is>
-      </c>
-      <c r="G163" t="inlineStr"/>
+          <t>Translocation</t>
+        </is>
+      </c>
+      <c r="G163" t="n">
+        <v>6.25</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -4872,21 +4872,19 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>chr16</t>
+          <t>chr12</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>47600000</v>
+        <v>95600000</v>
       </c>
       <c r="E164" t="inlineStr"/>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Translocation</t>
-        </is>
-      </c>
-      <c r="G164" t="n">
-        <v>9.380000000000001</v>
-      </c>
+          <t>SCE</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -4901,19 +4899,21 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>chr5</t>
+          <t>chr16</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>25000000</v>
+        <v>47600000</v>
       </c>
       <c r="E165" t="inlineStr"/>
       <c r="F165" t="inlineStr">
         <is>
-          <t>SCE</t>
-        </is>
-      </c>
-      <c r="G165" t="inlineStr"/>
+          <t>Translocation</t>
+        </is>
+      </c>
+      <c r="G165" t="n">
+        <v>9.380000000000001</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -4928,11 +4928,11 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>chr8</t>
+          <t>chr5</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>22000000</v>
+        <v>25000000</v>
       </c>
       <c r="E166" t="inlineStr"/>
       <c r="F166" t="inlineStr">
@@ -4955,11 +4955,11 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>chr9</t>
+          <t>chr8</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>6000000</v>
+        <v>22000000</v>
       </c>
       <c r="E167" t="inlineStr"/>
       <c r="F167" t="inlineStr">
@@ -4982,11 +4982,11 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>chrX</t>
+          <t>chr9</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>97600000</v>
+        <v>6000000</v>
       </c>
       <c r="E168" t="inlineStr"/>
       <c r="F168" t="inlineStr">
@@ -5004,16 +5004,16 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G38</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G37</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>chr13</t>
+          <t>chrX</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>72200000</v>
+        <v>97600000</v>
       </c>
       <c r="E169" t="inlineStr"/>
       <c r="F169" t="inlineStr">
@@ -5040,7 +5040,7 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>81400000</v>
+        <v>72200000</v>
       </c>
       <c r="E170" t="inlineStr"/>
       <c r="F170" t="inlineStr">
@@ -5063,11 +5063,11 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>chr2</t>
+          <t>chr13</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>19600000</v>
+        <v>81400000</v>
       </c>
       <c r="E171" t="inlineStr"/>
       <c r="F171" t="inlineStr">
@@ -5090,11 +5090,11 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>chr3</t>
+          <t>chr2</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>46200000</v>
+        <v>19600000</v>
       </c>
       <c r="E172" t="inlineStr"/>
       <c r="F172" t="inlineStr">
@@ -5117,11 +5117,11 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>chr6</t>
+          <t>chr3</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>162800000</v>
+        <v>46200000</v>
       </c>
       <c r="E173" t="inlineStr"/>
       <c r="F173" t="inlineStr">
@@ -5144,11 +5144,11 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>chr7</t>
+          <t>chr6</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>86800000</v>
+        <v>162800000</v>
       </c>
       <c r="E174" t="inlineStr"/>
       <c r="F174" t="inlineStr">
@@ -5171,11 +5171,11 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>chr8</t>
+          <t>chr7</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>117800000</v>
+        <v>86800000</v>
       </c>
       <c r="E175" t="inlineStr"/>
       <c r="F175" t="inlineStr">
@@ -5202,7 +5202,7 @@
         </is>
       </c>
       <c r="D176" t="n">
-        <v>120600000</v>
+        <v>117800000</v>
       </c>
       <c r="E176" t="inlineStr"/>
       <c r="F176" t="inlineStr">
@@ -5225,11 +5225,11 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>chrX</t>
+          <t>chr8</t>
         </is>
       </c>
       <c r="D177" t="n">
-        <v>149600000</v>
+        <v>120600000</v>
       </c>
       <c r="E177" t="inlineStr"/>
       <c r="F177" t="inlineStr">
@@ -5247,16 +5247,16 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G39</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G38</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>chr10</t>
+          <t>chrX</t>
         </is>
       </c>
       <c r="D178" t="n">
-        <v>86200000</v>
+        <v>149600000</v>
       </c>
       <c r="E178" t="inlineStr"/>
       <c r="F178" t="inlineStr">
@@ -5279,11 +5279,11 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>chr15</t>
+          <t>chr10</t>
         </is>
       </c>
       <c r="D179" t="n">
-        <v>36000000</v>
+        <v>86200000</v>
       </c>
       <c r="E179" t="inlineStr"/>
       <c r="F179" t="inlineStr">
@@ -5306,11 +5306,11 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>chr4</t>
+          <t>chr15</t>
         </is>
       </c>
       <c r="D180" t="n">
-        <v>55800000</v>
+        <v>36000000</v>
       </c>
       <c r="E180" t="inlineStr"/>
       <c r="F180" t="inlineStr">
@@ -5333,11 +5333,11 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>chr9</t>
+          <t>chr4</t>
         </is>
       </c>
       <c r="D181" t="n">
-        <v>11400000</v>
+        <v>55800000</v>
       </c>
       <c r="E181" t="inlineStr"/>
       <c r="F181" t="inlineStr">
@@ -5355,16 +5355,16 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G49</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G39</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>chr1</t>
+          <t>chr9</t>
         </is>
       </c>
       <c r="D182" t="n">
-        <v>98800000</v>
+        <v>11400000</v>
       </c>
       <c r="E182" t="inlineStr"/>
       <c r="F182" t="inlineStr">
@@ -5391,7 +5391,7 @@
         </is>
       </c>
       <c r="D183" t="n">
-        <v>104200000</v>
+        <v>98800000</v>
       </c>
       <c r="E183" t="inlineStr"/>
       <c r="F183" t="inlineStr">
@@ -5418,7 +5418,7 @@
         </is>
       </c>
       <c r="D184" t="n">
-        <v>107800000</v>
+        <v>104200000</v>
       </c>
       <c r="E184" t="inlineStr"/>
       <c r="F184" t="inlineStr">
@@ -5441,11 +5441,11 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>chr12</t>
+          <t>chr1</t>
         </is>
       </c>
       <c r="D185" t="n">
-        <v>13600000</v>
+        <v>107800000</v>
       </c>
       <c r="E185" t="inlineStr"/>
       <c r="F185" t="inlineStr">
@@ -5468,11 +5468,11 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>chr15</t>
+          <t>chr12</t>
         </is>
       </c>
       <c r="D186" t="n">
-        <v>27800000</v>
+        <v>13600000</v>
       </c>
       <c r="E186" t="inlineStr"/>
       <c r="F186" t="inlineStr">
@@ -5499,7 +5499,7 @@
         </is>
       </c>
       <c r="D187" t="n">
-        <v>70600000</v>
+        <v>27800000</v>
       </c>
       <c r="E187" t="inlineStr"/>
       <c r="F187" t="inlineStr">
@@ -5522,11 +5522,11 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>chr16</t>
+          <t>chr15</t>
         </is>
       </c>
       <c r="D188" t="n">
-        <v>59800000</v>
+        <v>70600000</v>
       </c>
       <c r="E188" t="inlineStr"/>
       <c r="F188" t="inlineStr">
@@ -5553,7 +5553,7 @@
         </is>
       </c>
       <c r="D189" t="n">
-        <v>65800000</v>
+        <v>59800000</v>
       </c>
       <c r="E189" t="inlineStr"/>
       <c r="F189" t="inlineStr">
@@ -5576,11 +5576,11 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>chr18</t>
+          <t>chr16</t>
         </is>
       </c>
       <c r="D190" t="n">
-        <v>31400000</v>
+        <v>65800000</v>
       </c>
       <c r="E190" t="inlineStr"/>
       <c r="F190" t="inlineStr">
@@ -5603,11 +5603,11 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>chr19</t>
+          <t>chr18</t>
         </is>
       </c>
       <c r="D191" t="n">
-        <v>19400000</v>
+        <v>31400000</v>
       </c>
       <c r="E191" t="inlineStr"/>
       <c r="F191" t="inlineStr">
@@ -5630,11 +5630,11 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>chr22</t>
+          <t>chr19</t>
         </is>
       </c>
       <c r="D192" t="n">
-        <v>24400000</v>
+        <v>19400000</v>
       </c>
       <c r="E192" t="inlineStr"/>
       <c r="F192" t="inlineStr">
@@ -5657,11 +5657,11 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>chr3</t>
+          <t>chr22</t>
         </is>
       </c>
       <c r="D193" t="n">
-        <v>147200000</v>
+        <v>24400000</v>
       </c>
       <c r="E193" t="inlineStr"/>
       <c r="F193" t="inlineStr">
@@ -5684,11 +5684,11 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>chr4</t>
+          <t>chr3</t>
         </is>
       </c>
       <c r="D194" t="n">
-        <v>107000000</v>
+        <v>147200000</v>
       </c>
       <c r="E194" t="inlineStr"/>
       <c r="F194" t="inlineStr">
@@ -5711,11 +5711,11 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>chr7</t>
+          <t>chr4</t>
         </is>
       </c>
       <c r="D195" t="n">
-        <v>130400000</v>
+        <v>107000000</v>
       </c>
       <c r="E195" t="inlineStr"/>
       <c r="F195" t="inlineStr">
@@ -5738,11 +5738,11 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>chr8</t>
+          <t>chr7</t>
         </is>
       </c>
       <c r="D196" t="n">
-        <v>27600000</v>
+        <v>130400000</v>
       </c>
       <c r="E196" t="inlineStr"/>
       <c r="F196" t="inlineStr">
@@ -5760,16 +5760,16 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G51</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G49</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>chr1</t>
+          <t>chr8</t>
         </is>
       </c>
       <c r="D197" t="n">
-        <v>76800000</v>
+        <v>27600000</v>
       </c>
       <c r="E197" t="inlineStr"/>
       <c r="F197" t="inlineStr">
@@ -5792,11 +5792,11 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>chr11</t>
+          <t>chr1</t>
         </is>
       </c>
       <c r="D198" t="n">
-        <v>57000000</v>
+        <v>76800000</v>
       </c>
       <c r="E198" t="inlineStr"/>
       <c r="F198" t="inlineStr">
@@ -5819,11 +5819,11 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>chr16</t>
+          <t>chr11</t>
         </is>
       </c>
       <c r="D199" t="n">
-        <v>11000000</v>
+        <v>57000000</v>
       </c>
       <c r="E199" t="inlineStr"/>
       <c r="F199" t="inlineStr">
@@ -5846,11 +5846,11 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>chr4</t>
+          <t>chr16</t>
         </is>
       </c>
       <c r="D200" t="n">
-        <v>149000000</v>
+        <v>11000000</v>
       </c>
       <c r="E200" t="inlineStr"/>
       <c r="F200" t="inlineStr">
@@ -5877,7 +5877,7 @@
         </is>
       </c>
       <c r="D201" t="n">
-        <v>158600000</v>
+        <v>149000000</v>
       </c>
       <c r="E201" t="inlineStr"/>
       <c r="F201" t="inlineStr">
@@ -5900,11 +5900,11 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>chr6</t>
+          <t>chr4</t>
         </is>
       </c>
       <c r="D202" t="n">
-        <v>155000000</v>
+        <v>158600000</v>
       </c>
       <c r="E202" t="inlineStr"/>
       <c r="F202" t="inlineStr">
@@ -5927,11 +5927,11 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>chr8</t>
+          <t>chr6</t>
         </is>
       </c>
       <c r="D203" t="n">
-        <v>98400000</v>
+        <v>155000000</v>
       </c>
       <c r="E203" t="inlineStr"/>
       <c r="F203" t="inlineStr">
@@ -5949,28 +5949,24 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G52</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G51</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>chr1</t>
+          <t>chr8</t>
         </is>
       </c>
       <c r="D204" t="n">
-        <v>147600000</v>
-      </c>
-      <c r="E204" t="n">
-        <v>149600000</v>
-      </c>
+        <v>98400000</v>
+      </c>
+      <c r="E204" t="inlineStr"/>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Inversion</t>
-        </is>
-      </c>
-      <c r="G204" t="n">
-        <v>6.25</v>
-      </c>
+          <t>SCE</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -5985,19 +5981,23 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>chr10</t>
+          <t>chr1</t>
         </is>
       </c>
       <c r="D205" t="n">
-        <v>37800000</v>
-      </c>
-      <c r="E205" t="inlineStr"/>
+        <v>147600000</v>
+      </c>
+      <c r="E205" t="n">
+        <v>149600000</v>
+      </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>SCE</t>
-        </is>
-      </c>
-      <c r="G205" t="inlineStr"/>
+          <t>Inversion</t>
+        </is>
+      </c>
+      <c r="G205" t="n">
+        <v>6.25</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -6012,11 +6012,11 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>chr12</t>
+          <t>chr10</t>
         </is>
       </c>
       <c r="D206" t="n">
-        <v>73600000</v>
+        <v>37800000</v>
       </c>
       <c r="E206" t="inlineStr"/>
       <c r="F206" t="inlineStr">
@@ -6039,11 +6039,11 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>chr16</t>
+          <t>chr12</t>
         </is>
       </c>
       <c r="D207" t="n">
-        <v>26000000</v>
+        <v>73600000</v>
       </c>
       <c r="E207" t="inlineStr"/>
       <c r="F207" t="inlineStr">
@@ -6066,11 +6066,11 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>chr2</t>
+          <t>chr16</t>
         </is>
       </c>
       <c r="D208" t="n">
-        <v>21400000</v>
+        <v>26000000</v>
       </c>
       <c r="E208" t="inlineStr"/>
       <c r="F208" t="inlineStr">
@@ -6093,11 +6093,11 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>chr20</t>
+          <t>chr2</t>
         </is>
       </c>
       <c r="D209" t="n">
-        <v>38800000</v>
+        <v>21400000</v>
       </c>
       <c r="E209" t="inlineStr"/>
       <c r="F209" t="inlineStr">
@@ -6120,11 +6120,11 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>chr3</t>
+          <t>chr20</t>
         </is>
       </c>
       <c r="D210" t="n">
-        <v>5800000</v>
+        <v>38800000</v>
       </c>
       <c r="E210" t="inlineStr"/>
       <c r="F210" t="inlineStr">
@@ -6147,11 +6147,11 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>chr5</t>
+          <t>chr3</t>
         </is>
       </c>
       <c r="D211" t="n">
-        <v>26400000</v>
+        <v>5800000</v>
       </c>
       <c r="E211" t="inlineStr"/>
       <c r="F211" t="inlineStr">
@@ -6178,7 +6178,7 @@
         </is>
       </c>
       <c r="D212" t="n">
-        <v>128800000</v>
+        <v>26400000</v>
       </c>
       <c r="E212" t="inlineStr"/>
       <c r="F212" t="inlineStr">
@@ -6201,21 +6201,19 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>chr9</t>
+          <t>chr5</t>
         </is>
       </c>
       <c r="D213" t="n">
-        <v>69400000</v>
+        <v>128800000</v>
       </c>
       <c r="E213" t="inlineStr"/>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Translocation</t>
-        </is>
-      </c>
-      <c r="G213" t="n">
-        <v>6.25</v>
-      </c>
+          <t>SCE</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -6234,15 +6232,17 @@
         </is>
       </c>
       <c r="D214" t="n">
-        <v>103000000</v>
+        <v>69400000</v>
       </c>
       <c r="E214" t="inlineStr"/>
       <c r="F214" t="inlineStr">
         <is>
-          <t>SCE</t>
-        </is>
-      </c>
-      <c r="G214" t="inlineStr"/>
+          <t>Translocation</t>
+        </is>
+      </c>
+      <c r="G214" t="n">
+        <v>6.25</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -6252,28 +6252,24 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G57</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G52</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>chr1</t>
+          <t>chr9</t>
         </is>
       </c>
       <c r="D215" t="n">
-        <v>147600000</v>
-      </c>
-      <c r="E215" t="n">
-        <v>149600000</v>
-      </c>
+        <v>103000000</v>
+      </c>
+      <c r="E215" t="inlineStr"/>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Inversion</t>
-        </is>
-      </c>
-      <c r="G215" t="n">
-        <v>6.25</v>
-      </c>
+          <t>SCE</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -6288,19 +6284,23 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>chr10</t>
+          <t>chr1</t>
         </is>
       </c>
       <c r="D216" t="n">
-        <v>35400000</v>
-      </c>
-      <c r="E216" t="inlineStr"/>
+        <v>147600000</v>
+      </c>
+      <c r="E216" t="n">
+        <v>149600000</v>
+      </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>SCE</t>
-        </is>
-      </c>
-      <c r="G216" t="inlineStr"/>
+          <t>Inversion</t>
+        </is>
+      </c>
+      <c r="G216" t="n">
+        <v>6.25</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -6315,11 +6315,11 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>chr14</t>
+          <t>chr10</t>
         </is>
       </c>
       <c r="D217" t="n">
-        <v>86000000</v>
+        <v>35400000</v>
       </c>
       <c r="E217" t="inlineStr"/>
       <c r="F217" t="inlineStr">
@@ -6342,11 +6342,11 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>chr16</t>
+          <t>chr14</t>
         </is>
       </c>
       <c r="D218" t="n">
-        <v>78200000</v>
+        <v>86000000</v>
       </c>
       <c r="E218" t="inlineStr"/>
       <c r="F218" t="inlineStr">
@@ -6369,11 +6369,11 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>chr17</t>
+          <t>chr16</t>
         </is>
       </c>
       <c r="D219" t="n">
-        <v>41600000</v>
+        <v>78200000</v>
       </c>
       <c r="E219" t="inlineStr"/>
       <c r="F219" t="inlineStr">
@@ -6396,11 +6396,11 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>chr19</t>
+          <t>chr17</t>
         </is>
       </c>
       <c r="D220" t="n">
-        <v>8200000</v>
+        <v>41600000</v>
       </c>
       <c r="E220" t="inlineStr"/>
       <c r="F220" t="inlineStr">
@@ -6423,11 +6423,11 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>chr2</t>
+          <t>chr19</t>
         </is>
       </c>
       <c r="D221" t="n">
-        <v>82400000</v>
+        <v>8200000</v>
       </c>
       <c r="E221" t="inlineStr"/>
       <c r="F221" t="inlineStr">
@@ -6454,7 +6454,7 @@
         </is>
       </c>
       <c r="D222" t="n">
-        <v>117800000</v>
+        <v>82400000</v>
       </c>
       <c r="E222" t="inlineStr"/>
       <c r="F222" t="inlineStr">
@@ -6477,11 +6477,11 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>chr4</t>
+          <t>chr2</t>
         </is>
       </c>
       <c r="D223" t="n">
-        <v>143200000</v>
+        <v>117800000</v>
       </c>
       <c r="E223" t="inlineStr"/>
       <c r="F223" t="inlineStr">
@@ -6504,11 +6504,11 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>chr5</t>
+          <t>chr4</t>
         </is>
       </c>
       <c r="D224" t="n">
-        <v>117000000</v>
+        <v>143200000</v>
       </c>
       <c r="E224" t="inlineStr"/>
       <c r="F224" t="inlineStr">
@@ -6531,11 +6531,11 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>chr6</t>
+          <t>chr5</t>
         </is>
       </c>
       <c r="D225" t="n">
-        <v>138600000</v>
+        <v>117000000</v>
       </c>
       <c r="E225" t="inlineStr"/>
       <c r="F225" t="inlineStr">
@@ -6558,11 +6558,11 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>chr8</t>
+          <t>chr6</t>
         </is>
       </c>
       <c r="D226" t="n">
-        <v>64200000</v>
+        <v>138600000</v>
       </c>
       <c r="E226" t="inlineStr"/>
       <c r="F226" t="inlineStr">
@@ -6585,11 +6585,11 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>chr9</t>
+          <t>chr8</t>
         </is>
       </c>
       <c r="D227" t="n">
-        <v>94600000</v>
+        <v>64200000</v>
       </c>
       <c r="E227" t="inlineStr"/>
       <c r="F227" t="inlineStr">
@@ -6616,7 +6616,7 @@
         </is>
       </c>
       <c r="D228" t="n">
-        <v>128000000</v>
+        <v>94600000</v>
       </c>
       <c r="E228" t="inlineStr"/>
       <c r="F228" t="inlineStr">
@@ -6639,11 +6639,11 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>chrX</t>
+          <t>chr9</t>
         </is>
       </c>
       <c r="D229" t="n">
-        <v>90400000</v>
+        <v>128000000</v>
       </c>
       <c r="E229" t="inlineStr"/>
       <c r="F229" t="inlineStr">
@@ -6661,16 +6661,16 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G61</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G57</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>chr10</t>
+          <t>chrX</t>
         </is>
       </c>
       <c r="D230" t="n">
-        <v>5800000</v>
+        <v>90400000</v>
       </c>
       <c r="E230" t="inlineStr"/>
       <c r="F230" t="inlineStr">
@@ -6693,11 +6693,11 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>chr11</t>
+          <t>chr10</t>
         </is>
       </c>
       <c r="D231" t="n">
-        <v>58000000</v>
+        <v>5800000</v>
       </c>
       <c r="E231" t="inlineStr"/>
       <c r="F231" t="inlineStr">
@@ -6720,11 +6720,11 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>chr12</t>
+          <t>chr11</t>
         </is>
       </c>
       <c r="D232" t="n">
-        <v>42800000</v>
+        <v>58000000</v>
       </c>
       <c r="E232" t="inlineStr"/>
       <c r="F232" t="inlineStr">
@@ -6747,11 +6747,11 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>chr14</t>
+          <t>chr12</t>
         </is>
       </c>
       <c r="D233" t="n">
-        <v>54200000</v>
+        <v>42800000</v>
       </c>
       <c r="E233" t="inlineStr"/>
       <c r="F233" t="inlineStr">
@@ -6774,21 +6774,19 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>chr16</t>
+          <t>chr14</t>
         </is>
       </c>
       <c r="D234" t="n">
-        <v>47600000</v>
+        <v>54200000</v>
       </c>
       <c r="E234" t="inlineStr"/>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Translocation</t>
-        </is>
-      </c>
-      <c r="G234" t="n">
-        <v>9.380000000000001</v>
-      </c>
+          <t>SCE</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -6803,19 +6801,21 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>chr19</t>
+          <t>chr16</t>
         </is>
       </c>
       <c r="D235" t="n">
-        <v>28200000</v>
+        <v>47600000</v>
       </c>
       <c r="E235" t="inlineStr"/>
       <c r="F235" t="inlineStr">
         <is>
-          <t>SCE</t>
-        </is>
-      </c>
-      <c r="G235" t="inlineStr"/>
+          <t>Translocation</t>
+        </is>
+      </c>
+      <c r="G235" t="n">
+        <v>9.380000000000001</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -6834,7 +6834,7 @@
         </is>
       </c>
       <c r="D236" t="n">
-        <v>39800000</v>
+        <v>28200000</v>
       </c>
       <c r="E236" t="inlineStr"/>
       <c r="F236" t="inlineStr">
@@ -6857,11 +6857,11 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>chr22</t>
+          <t>chr19</t>
         </is>
       </c>
       <c r="D237" t="n">
-        <v>27000000</v>
+        <v>39800000</v>
       </c>
       <c r="E237" t="inlineStr"/>
       <c r="F237" t="inlineStr">
@@ -6884,11 +6884,11 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>chr3</t>
+          <t>chr22</t>
         </is>
       </c>
       <c r="D238" t="n">
-        <v>176400000</v>
+        <v>27000000</v>
       </c>
       <c r="E238" t="inlineStr"/>
       <c r="F238" t="inlineStr">
@@ -6911,11 +6911,11 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>chr5</t>
+          <t>chr3</t>
         </is>
       </c>
       <c r="D239" t="n">
-        <v>83200000</v>
+        <v>176400000</v>
       </c>
       <c r="E239" t="inlineStr"/>
       <c r="F239" t="inlineStr">
@@ -6938,11 +6938,11 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>chr7</t>
+          <t>chr5</t>
         </is>
       </c>
       <c r="D240" t="n">
-        <v>12400000</v>
+        <v>83200000</v>
       </c>
       <c r="E240" t="inlineStr"/>
       <c r="F240" t="inlineStr">
@@ -6965,11 +6965,11 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>chr8</t>
+          <t>chr7</t>
         </is>
       </c>
       <c r="D241" t="n">
-        <v>44800000</v>
+        <v>12400000</v>
       </c>
       <c r="E241" t="inlineStr"/>
       <c r="F241" t="inlineStr">
@@ -6992,11 +6992,11 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>chrX</t>
+          <t>chr8</t>
         </is>
       </c>
       <c r="D242" t="n">
-        <v>154200000</v>
+        <v>44800000</v>
       </c>
       <c r="E242" t="inlineStr"/>
       <c r="F242" t="inlineStr">
@@ -7014,16 +7014,16 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G63</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G61</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>chr1</t>
+          <t>chrX</t>
         </is>
       </c>
       <c r="D243" t="n">
-        <v>212600000</v>
+        <v>154200000</v>
       </c>
       <c r="E243" t="inlineStr"/>
       <c r="F243" t="inlineStr">
@@ -7046,11 +7046,11 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>chr10</t>
+          <t>chr1</t>
         </is>
       </c>
       <c r="D244" t="n">
-        <v>28400000</v>
+        <v>212600000</v>
       </c>
       <c r="E244" t="inlineStr"/>
       <c r="F244" t="inlineStr">
@@ -7077,7 +7077,7 @@
         </is>
       </c>
       <c r="D245" t="n">
-        <v>128000000</v>
+        <v>28400000</v>
       </c>
       <c r="E245" t="inlineStr"/>
       <c r="F245" t="inlineStr">
@@ -7100,11 +7100,11 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>chr11</t>
+          <t>chr10</t>
         </is>
       </c>
       <c r="D246" t="n">
-        <v>102600000</v>
+        <v>128000000</v>
       </c>
       <c r="E246" t="inlineStr"/>
       <c r="F246" t="inlineStr">
@@ -7127,11 +7127,11 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>chr14</t>
+          <t>chr11</t>
         </is>
       </c>
       <c r="D247" t="n">
-        <v>33400000</v>
+        <v>102600000</v>
       </c>
       <c r="E247" t="inlineStr"/>
       <c r="F247" t="inlineStr">
@@ -7154,11 +7154,11 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>chr16</t>
+          <t>chr14</t>
         </is>
       </c>
       <c r="D248" t="n">
-        <v>83800000</v>
+        <v>33400000</v>
       </c>
       <c r="E248" t="inlineStr"/>
       <c r="F248" t="inlineStr">
@@ -7181,11 +7181,11 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>chr17</t>
+          <t>chr16</t>
         </is>
       </c>
       <c r="D249" t="n">
-        <v>65600000</v>
+        <v>83800000</v>
       </c>
       <c r="E249" t="inlineStr"/>
       <c r="F249" t="inlineStr">
@@ -7203,16 +7203,16 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G64</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G63</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>chr1</t>
+          <t>chr17</t>
         </is>
       </c>
       <c r="D250" t="n">
-        <v>231800000</v>
+        <v>65600000</v>
       </c>
       <c r="E250" t="inlineStr"/>
       <c r="F250" t="inlineStr">
@@ -7235,11 +7235,11 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>chr10</t>
+          <t>chr1</t>
         </is>
       </c>
       <c r="D251" t="n">
-        <v>112800000</v>
+        <v>231800000</v>
       </c>
       <c r="E251" t="inlineStr"/>
       <c r="F251" t="inlineStr">
@@ -7262,11 +7262,11 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>chr11</t>
+          <t>chr10</t>
         </is>
       </c>
       <c r="D252" t="n">
-        <v>55600000</v>
+        <v>112800000</v>
       </c>
       <c r="E252" t="inlineStr"/>
       <c r="F252" t="inlineStr">
@@ -7289,11 +7289,11 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>chr12</t>
+          <t>chr11</t>
         </is>
       </c>
       <c r="D253" t="n">
-        <v>111000000</v>
+        <v>55600000</v>
       </c>
       <c r="E253" t="inlineStr"/>
       <c r="F253" t="inlineStr">
@@ -7316,11 +7316,11 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>chr16</t>
+          <t>chr12</t>
         </is>
       </c>
       <c r="D254" t="n">
-        <v>24000000</v>
+        <v>111000000</v>
       </c>
       <c r="E254" t="inlineStr"/>
       <c r="F254" t="inlineStr">
@@ -7343,11 +7343,11 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>chr2</t>
+          <t>chr16</t>
         </is>
       </c>
       <c r="D255" t="n">
-        <v>138200000</v>
+        <v>24000000</v>
       </c>
       <c r="E255" t="inlineStr"/>
       <c r="F255" t="inlineStr">
@@ -7370,11 +7370,11 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>chr5</t>
+          <t>chr2</t>
         </is>
       </c>
       <c r="D256" t="n">
-        <v>98200000</v>
+        <v>138200000</v>
       </c>
       <c r="E256" t="inlineStr"/>
       <c r="F256" t="inlineStr">
@@ -7397,11 +7397,11 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>chr6</t>
+          <t>chr5</t>
         </is>
       </c>
       <c r="D257" t="n">
-        <v>64000000</v>
+        <v>98200000</v>
       </c>
       <c r="E257" t="inlineStr"/>
       <c r="F257" t="inlineStr">
@@ -7424,11 +7424,11 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>chrX</t>
+          <t>chr6</t>
         </is>
       </c>
       <c r="D258" t="n">
-        <v>37400000</v>
+        <v>64000000</v>
       </c>
       <c r="E258" t="inlineStr"/>
       <c r="F258" t="inlineStr">
@@ -7446,16 +7446,16 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G74</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G64</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>chr1</t>
+          <t>chrX</t>
         </is>
       </c>
       <c r="D259" t="n">
-        <v>242400000</v>
+        <v>37400000</v>
       </c>
       <c r="E259" t="inlineStr"/>
       <c r="F259" t="inlineStr">
@@ -7478,11 +7478,11 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>chr10</t>
+          <t>chr1</t>
         </is>
       </c>
       <c r="D260" t="n">
-        <v>97600000</v>
+        <v>242400000</v>
       </c>
       <c r="E260" t="inlineStr"/>
       <c r="F260" t="inlineStr">
@@ -7505,11 +7505,11 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>chr12</t>
+          <t>chr10</t>
         </is>
       </c>
       <c r="D261" t="n">
-        <v>120600000</v>
+        <v>97600000</v>
       </c>
       <c r="E261" t="inlineStr"/>
       <c r="F261" t="inlineStr">
@@ -7532,21 +7532,19 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>chr13</t>
+          <t>chr12</t>
         </is>
       </c>
       <c r="D262" t="n">
-        <v>18400000</v>
+        <v>120600000</v>
       </c>
       <c r="E262" t="inlineStr"/>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Translocation</t>
-        </is>
-      </c>
-      <c r="G262" t="n">
-        <v>9.380000000000001</v>
-      </c>
+          <t>SCE</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -7565,15 +7563,17 @@
         </is>
       </c>
       <c r="D263" t="n">
-        <v>82600000</v>
+        <v>18400000</v>
       </c>
       <c r="E263" t="inlineStr"/>
       <c r="F263" t="inlineStr">
         <is>
-          <t>SCE</t>
-        </is>
-      </c>
-      <c r="G263" t="inlineStr"/>
+          <t>Translocation</t>
+        </is>
+      </c>
+      <c r="G263" t="n">
+        <v>9.380000000000001</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -7592,7 +7592,7 @@
         </is>
       </c>
       <c r="D264" t="n">
-        <v>104800000</v>
+        <v>82600000</v>
       </c>
       <c r="E264" t="inlineStr"/>
       <c r="F264" t="inlineStr">
@@ -7615,11 +7615,11 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>chr2</t>
+          <t>chr13</t>
         </is>
       </c>
       <c r="D265" t="n">
-        <v>82000000</v>
+        <v>104800000</v>
       </c>
       <c r="E265" t="inlineStr"/>
       <c r="F265" t="inlineStr">
@@ -7642,11 +7642,11 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>chr22</t>
+          <t>chr2</t>
         </is>
       </c>
       <c r="D266" t="n">
-        <v>33600000</v>
+        <v>82000000</v>
       </c>
       <c r="E266" t="inlineStr"/>
       <c r="F266" t="inlineStr">
@@ -7669,21 +7669,19 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>chr5</t>
+          <t>chr22</t>
         </is>
       </c>
       <c r="D267" t="n">
-        <v>71400000</v>
+        <v>33600000</v>
       </c>
       <c r="E267" t="inlineStr"/>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Translocation</t>
-        </is>
-      </c>
-      <c r="G267" t="n">
-        <v>6.25</v>
-      </c>
+          <t>SCE</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -7702,15 +7700,17 @@
         </is>
       </c>
       <c r="D268" t="n">
-        <v>125400000</v>
+        <v>71400000</v>
       </c>
       <c r="E268" t="inlineStr"/>
       <c r="F268" t="inlineStr">
         <is>
-          <t>SCE</t>
-        </is>
-      </c>
-      <c r="G268" t="inlineStr"/>
+          <t>Translocation</t>
+        </is>
+      </c>
+      <c r="G268" t="n">
+        <v>6.25</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -7725,11 +7725,11 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>chr6</t>
+          <t>chr5</t>
         </is>
       </c>
       <c r="D269" t="n">
-        <v>81400000</v>
+        <v>125400000</v>
       </c>
       <c r="E269" t="inlineStr"/>
       <c r="F269" t="inlineStr">
@@ -7756,7 +7756,7 @@
         </is>
       </c>
       <c r="D270" t="n">
-        <v>115200000</v>
+        <v>81400000</v>
       </c>
       <c r="E270" t="inlineStr"/>
       <c r="F270" t="inlineStr">
@@ -7783,7 +7783,7 @@
         </is>
       </c>
       <c r="D271" t="n">
-        <v>166400000</v>
+        <v>115200000</v>
       </c>
       <c r="E271" t="inlineStr"/>
       <c r="F271" t="inlineStr">
@@ -7801,16 +7801,16 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G81</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G74</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>chr1</t>
+          <t>chr6</t>
         </is>
       </c>
       <c r="D272" t="n">
-        <v>86400000</v>
+        <v>166400000</v>
       </c>
       <c r="E272" t="inlineStr"/>
       <c r="F272" t="inlineStr">
@@ -7837,7 +7837,7 @@
         </is>
       </c>
       <c r="D273" t="n">
-        <v>210000000</v>
+        <v>86400000</v>
       </c>
       <c r="E273" t="inlineStr"/>
       <c r="F273" t="inlineStr">
@@ -7860,11 +7860,11 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>chr10</t>
+          <t>chr1</t>
         </is>
       </c>
       <c r="D274" t="n">
-        <v>54400000</v>
+        <v>210000000</v>
       </c>
       <c r="E274" t="inlineStr"/>
       <c r="F274" t="inlineStr">
@@ -7887,11 +7887,11 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>chr14</t>
+          <t>chr10</t>
         </is>
       </c>
       <c r="D275" t="n">
-        <v>22400000</v>
+        <v>54400000</v>
       </c>
       <c r="E275" t="inlineStr"/>
       <c r="F275" t="inlineStr">
@@ -7918,7 +7918,7 @@
         </is>
       </c>
       <c r="D276" t="n">
-        <v>43600000</v>
+        <v>22400000</v>
       </c>
       <c r="E276" t="inlineStr"/>
       <c r="F276" t="inlineStr">
@@ -7941,11 +7941,11 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>chr2</t>
+          <t>chr14</t>
         </is>
       </c>
       <c r="D277" t="n">
-        <v>163200000</v>
+        <v>43600000</v>
       </c>
       <c r="E277" t="inlineStr"/>
       <c r="F277" t="inlineStr">
@@ -7968,11 +7968,11 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>chr3</t>
+          <t>chr2</t>
         </is>
       </c>
       <c r="D278" t="n">
-        <v>84800000</v>
+        <v>163200000</v>
       </c>
       <c r="E278" t="inlineStr"/>
       <c r="F278" t="inlineStr">
@@ -7995,11 +7995,11 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>chr5</t>
+          <t>chr3</t>
         </is>
       </c>
       <c r="D279" t="n">
-        <v>41600000</v>
+        <v>84800000</v>
       </c>
       <c r="E279" t="inlineStr"/>
       <c r="F279" t="inlineStr">
@@ -8022,11 +8022,11 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>chr6</t>
+          <t>chr5</t>
         </is>
       </c>
       <c r="D280" t="n">
-        <v>90200000</v>
+        <v>41600000</v>
       </c>
       <c r="E280" t="inlineStr"/>
       <c r="F280" t="inlineStr">
@@ -8049,11 +8049,11 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>chr8</t>
+          <t>chr6</t>
         </is>
       </c>
       <c r="D281" t="n">
-        <v>29000000</v>
+        <v>90200000</v>
       </c>
       <c r="E281" t="inlineStr"/>
       <c r="F281" t="inlineStr">
@@ -8080,7 +8080,7 @@
         </is>
       </c>
       <c r="D282" t="n">
-        <v>85800000</v>
+        <v>29000000</v>
       </c>
       <c r="E282" t="inlineStr"/>
       <c r="F282" t="inlineStr">
@@ -8103,11 +8103,11 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>chrX</t>
+          <t>chr8</t>
         </is>
       </c>
       <c r="D283" t="n">
-        <v>117200000</v>
+        <v>85800000</v>
       </c>
       <c r="E283" t="inlineStr"/>
       <c r="F283" t="inlineStr">
@@ -8125,16 +8125,16 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G86</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G81</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>chr10</t>
+          <t>chrX</t>
         </is>
       </c>
       <c r="D284" t="n">
-        <v>60000000</v>
+        <v>117200000</v>
       </c>
       <c r="E284" t="inlineStr"/>
       <c r="F284" t="inlineStr">
@@ -8157,11 +8157,11 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>chr13</t>
+          <t>chr10</t>
         </is>
       </c>
       <c r="D285" t="n">
-        <v>55200000</v>
+        <v>60000000</v>
       </c>
       <c r="E285" t="inlineStr"/>
       <c r="F285" t="inlineStr">
@@ -8184,11 +8184,11 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>chr15</t>
+          <t>chr13</t>
         </is>
       </c>
       <c r="D286" t="n">
-        <v>60200000</v>
+        <v>55200000</v>
       </c>
       <c r="E286" t="inlineStr"/>
       <c r="F286" t="inlineStr">
@@ -8211,11 +8211,11 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>chr19</t>
+          <t>chr15</t>
         </is>
       </c>
       <c r="D287" t="n">
-        <v>38800000</v>
+        <v>60200000</v>
       </c>
       <c r="E287" t="inlineStr"/>
       <c r="F287" t="inlineStr">
@@ -8238,11 +8238,11 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>chr2</t>
+          <t>chr19</t>
         </is>
       </c>
       <c r="D288" t="n">
-        <v>214800000</v>
+        <v>38800000</v>
       </c>
       <c r="E288" t="inlineStr"/>
       <c r="F288" t="inlineStr">
@@ -8265,11 +8265,11 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>chr21</t>
+          <t>chr2</t>
         </is>
       </c>
       <c r="D289" t="n">
-        <v>24200000</v>
+        <v>214800000</v>
       </c>
       <c r="E289" t="inlineStr"/>
       <c r="F289" t="inlineStr">
@@ -8292,11 +8292,11 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>chr22</t>
+          <t>chr21</t>
         </is>
       </c>
       <c r="D290" t="n">
-        <v>32200000</v>
+        <v>24200000</v>
       </c>
       <c r="E290" t="inlineStr"/>
       <c r="F290" t="inlineStr">
@@ -8319,11 +8319,11 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>chr4</t>
+          <t>chr22</t>
         </is>
       </c>
       <c r="D291" t="n">
-        <v>12800000</v>
+        <v>32200000</v>
       </c>
       <c r="E291" t="inlineStr"/>
       <c r="F291" t="inlineStr">
@@ -8350,7 +8350,7 @@
         </is>
       </c>
       <c r="D292" t="n">
-        <v>15600000</v>
+        <v>12800000</v>
       </c>
       <c r="E292" t="inlineStr"/>
       <c r="F292" t="inlineStr">
@@ -8373,11 +8373,11 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>chr9</t>
+          <t>chr4</t>
         </is>
       </c>
       <c r="D293" t="n">
-        <v>33200000</v>
+        <v>15600000</v>
       </c>
       <c r="E293" t="inlineStr"/>
       <c r="F293" t="inlineStr">
@@ -8395,16 +8395,16 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G91</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G86</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>chr11</t>
+          <t>chr8</t>
         </is>
       </c>
       <c r="D294" t="n">
-        <v>109600000</v>
+        <v>47000000</v>
       </c>
       <c r="E294" t="inlineStr"/>
       <c r="F294" t="inlineStr">
@@ -8422,26 +8422,24 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G91</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G86</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>chr13</t>
+          <t>chr9</t>
         </is>
       </c>
       <c r="D295" t="n">
-        <v>18400000</v>
+        <v>33200000</v>
       </c>
       <c r="E295" t="inlineStr"/>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Translocation</t>
-        </is>
-      </c>
-      <c r="G295" t="n">
-        <v>9.380000000000001</v>
-      </c>
+          <t>SCE</t>
+        </is>
+      </c>
+      <c r="G295" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -8456,11 +8454,11 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>chr14</t>
+          <t>chr11</t>
         </is>
       </c>
       <c r="D296" t="n">
-        <v>94200000</v>
+        <v>109600000</v>
       </c>
       <c r="E296" t="inlineStr"/>
       <c r="F296" t="inlineStr">
@@ -8483,19 +8481,21 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>chr2</t>
+          <t>chr13</t>
         </is>
       </c>
       <c r="D297" t="n">
-        <v>9400000</v>
+        <v>18400000</v>
       </c>
       <c r="E297" t="inlineStr"/>
       <c r="F297" t="inlineStr">
         <is>
-          <t>SCE</t>
-        </is>
-      </c>
-      <c r="G297" t="inlineStr"/>
+          <t>Translocation</t>
+        </is>
+      </c>
+      <c r="G297" t="n">
+        <v>9.380000000000001</v>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -8510,11 +8510,11 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>chr21</t>
+          <t>chr14</t>
         </is>
       </c>
       <c r="D298" t="n">
-        <v>27000000</v>
+        <v>94200000</v>
       </c>
       <c r="E298" t="inlineStr"/>
       <c r="F298" t="inlineStr">
@@ -8537,11 +8537,11 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>chr3</t>
+          <t>chr2</t>
         </is>
       </c>
       <c r="D299" t="n">
-        <v>118000000</v>
+        <v>9400000</v>
       </c>
       <c r="E299" t="inlineStr"/>
       <c r="F299" t="inlineStr">
@@ -8564,11 +8564,11 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>chr5</t>
+          <t>chr21</t>
         </is>
       </c>
       <c r="D300" t="n">
-        <v>8600000</v>
+        <v>27000000</v>
       </c>
       <c r="E300" t="inlineStr"/>
       <c r="F300" t="inlineStr">
@@ -8591,11 +8591,11 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>chrX</t>
+          <t>chr3</t>
         </is>
       </c>
       <c r="D301" t="n">
-        <v>129000000</v>
+        <v>118000000</v>
       </c>
       <c r="E301" t="inlineStr"/>
       <c r="F301" t="inlineStr">
@@ -8613,16 +8613,16 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G92</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G91</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>chr12</t>
+          <t>chr5</t>
         </is>
       </c>
       <c r="D302" t="n">
-        <v>38400000</v>
+        <v>8600000</v>
       </c>
       <c r="E302" t="inlineStr"/>
       <c r="F302" t="inlineStr">
@@ -8640,16 +8640,16 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G92</t>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G91</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>chr12</t>
+          <t>chrX</t>
         </is>
       </c>
       <c r="D303" t="n">
-        <v>97400000</v>
+        <v>129000000</v>
       </c>
       <c r="E303" t="inlineStr"/>
       <c r="F303" t="inlineStr">
@@ -8672,11 +8672,11 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>chr13</t>
+          <t>chr12</t>
         </is>
       </c>
       <c r="D304" t="n">
-        <v>72400000</v>
+        <v>38400000</v>
       </c>
       <c r="E304" t="inlineStr"/>
       <c r="F304" t="inlineStr">
@@ -8699,11 +8699,11 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>chr13</t>
+          <t>chr12</t>
         </is>
       </c>
       <c r="D305" t="n">
-        <v>81800000</v>
+        <v>97400000</v>
       </c>
       <c r="E305" t="inlineStr"/>
       <c r="F305" t="inlineStr">
@@ -8730,7 +8730,7 @@
         </is>
       </c>
       <c r="D306" t="n">
-        <v>93800000</v>
+        <v>72400000</v>
       </c>
       <c r="E306" t="inlineStr"/>
       <c r="F306" t="inlineStr">
@@ -8753,11 +8753,11 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>chr14</t>
+          <t>chr13</t>
         </is>
       </c>
       <c r="D307" t="n">
-        <v>79600000</v>
+        <v>81800000</v>
       </c>
       <c r="E307" t="inlineStr"/>
       <c r="F307" t="inlineStr">
@@ -8780,11 +8780,11 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>chr16</t>
+          <t>chr13</t>
         </is>
       </c>
       <c r="D308" t="n">
-        <v>59400000</v>
+        <v>93800000</v>
       </c>
       <c r="E308" t="inlineStr"/>
       <c r="F308" t="inlineStr">
@@ -8807,11 +8807,11 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>chr16</t>
+          <t>chr14</t>
         </is>
       </c>
       <c r="D309" t="n">
-        <v>66000000</v>
+        <v>79600000</v>
       </c>
       <c r="E309" t="inlineStr"/>
       <c r="F309" t="inlineStr">
@@ -8834,11 +8834,11 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>chr2</t>
+          <t>chr16</t>
         </is>
       </c>
       <c r="D310" t="n">
-        <v>106000000</v>
+        <v>59400000</v>
       </c>
       <c r="E310" t="inlineStr"/>
       <c r="F310" t="inlineStr">
@@ -8861,11 +8861,11 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>chr2</t>
+          <t>chr16</t>
         </is>
       </c>
       <c r="D311" t="n">
-        <v>190600000</v>
+        <v>66000000</v>
       </c>
       <c r="E311" t="inlineStr"/>
       <c r="F311" t="inlineStr">
@@ -8888,11 +8888,11 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>chr20</t>
+          <t>chr2</t>
         </is>
       </c>
       <c r="D312" t="n">
-        <v>14000000</v>
+        <v>106000000</v>
       </c>
       <c r="E312" t="inlineStr"/>
       <c r="F312" t="inlineStr">
@@ -8915,11 +8915,11 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>chr6</t>
+          <t>chr2</t>
         </is>
       </c>
       <c r="D313" t="n">
-        <v>21600000</v>
+        <v>190600000</v>
       </c>
       <c r="E313" t="inlineStr"/>
       <c r="F313" t="inlineStr">
@@ -8942,11 +8942,11 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>chrX</t>
+          <t>chr20</t>
         </is>
       </c>
       <c r="D314" t="n">
-        <v>58600000</v>
+        <v>14000000</v>
       </c>
       <c r="E314" t="inlineStr"/>
       <c r="F314" t="inlineStr">
@@ -8955,6 +8955,60 @@
         </is>
       </c>
       <c r="G314" t="inlineStr"/>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>fastq0022_HPNE_M</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G92</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>chr6</t>
+        </is>
+      </c>
+      <c r="D315" t="n">
+        <v>21600000</v>
+      </c>
+      <c r="E315" t="inlineStr"/>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>SCE</t>
+        </is>
+      </c>
+      <c r="G315" t="inlineStr"/>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>fastq0022_HPNE_M</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>HCJY7AFX7_MIxT1XT3_24s001577-1-1_Jeong_lane1MixiTRU7G92</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>chrX</t>
+        </is>
+      </c>
+      <c r="D316" t="n">
+        <v>58600000</v>
+      </c>
+      <c r="E316" t="inlineStr"/>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>SCE</t>
+        </is>
+      </c>
+      <c r="G316" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
